--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -467,12 +467,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cancer Survivor Uses Her Diagnosis To Justify A Hall Pass Request That Ends Her 20-Year Marriage</t>
+          <t>55 Doctors Reveal The Health Problems Showing Up More Than Ever Before</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0001-cancer-survivor-uses-her-diagnosis-to-justify-a-hall-pass-re.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0001-55-doctors-reveal-the-health-problems-showing-up-more-than-e.jpg</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15 Real-Life Bizarre Accidents That Sound Fake, But Ultimately Took The Lives Of Innocent People</t>
+          <t>“This Hurts My Eyes”: 50 Attempts That Were Made But They Were Not Good Enough (New Pics)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0002-15-real-life-bizarre-accidents-that-sound-fake-but-ultimatel.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0002-this-hurts-my-eyes-50-attempts-that-were-made-but-they-were-.jpg</t>
         </is>
       </c>
     </row>
@@ -497,12 +497,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>“Apologize For What?” GF Accuses BF Of Cheating After He Bearhugged Friend Having Breakdown</t>
+          <t>Bride Asks Mom Why She Wants The Wedding Delayed, Doesn’t Like The Answer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0003-apologize-for-what-gf-accuses-bf-of-cheating-after-he-bearhu.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0003-bride-asks-mom-why-she-wants-the-wedding-delayed-doesnt-like.jpg</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Family’s Goodbye Visit Turns Chaotic When Grandma Won’t Leave And Takes Hold Of Toddler</t>
+          <t>Woman Refuses To Spend Vacation Babysitting Sister’s Kids, Family Drama Follows</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0004-familys-goodbye-visit-turns-chaotic-when-grandma-wont-leave-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0004-woman-refuses-to-spend-vacation-babysitting-sisters-kids-fam.jpg</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21 Prime Day Outdoor And Backyard Essentials That Are About To Make Your Summer So Much Better</t>
+          <t>If You Answer All 21 General Knowledge Questions, You’re Basically A Walking Encyclopedia</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0005-21-prime-day-outdoor-and-backyard-essentials-that-are-about-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0005-if-you-answer-all-21-general-knowledge-questions-youre-basic.jpg</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>“This Isn’t Over”: In-Laws Treat Couple’s Home As Redecoration Project, Mad When DIL Bans Them</t>
+          <t>Daily Guess The Timeline Game #087 (Jun 18, 2026)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0006-this-isnt-over-in-laws-treat-couples-home-as-redecoration-pr.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0006-daily-guess-the-timeline-game-087-jun-18-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -557,12 +557,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>After Weeks Of Planning And Childcare Arrangements, Woman Discovers Group Hike Wasn’t Really A Hike</t>
+          <t>Narcissistic Parents: A Survival Guide for Adult Children</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0007-after-weeks-of-planning-and-childcare-arrangements-woman-dis.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0007-narcissistic-parents-a-survival-guide-for-adult-children.jpg</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>“[AITJ] For Turning Down A Family Vacation Because I Would Have To Pay And My Sister Wouldn’t?”</t>
+          <t>Only A Well-Read Person Can Answer All 20 Of These Questions On Classic Literature</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0008-aitj-for-turning-down-a-family-vacation-because-i-would-have.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0008-only-a-well-read-person-can-answer-all-20-of-these-questions.jpg</t>
         </is>
       </c>
     </row>
@@ -587,12 +587,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>“Am I The Jerk For Calling The Cops To Remove My Ex-Wife From My Home?”</t>
+          <t>Shelter Dogs Are Finding New Homes After This Man Gives Them Backpack Rides Around NYC</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0009-am-i-the-jerk-for-calling-the-cops-to-remove-my-ex-wife-from.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0009-shelter-dogs-are-finding-new-homes-after-this-man-gives-them.jpg</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>“Can’t Expect Much”: Guy Is Shocked Kids Don’t See Him As A Father, Ex-Wife Tells Him Exactly Why</t>
+          <t>Daily Guess The Country Game #033 (Jun 18, 2026)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0010-cant-expect-much-guy-is-shocked-kids-dont-see-him-as-a-fathe.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0010-daily-guess-the-country-game-033-jun-18-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Man Feels Abandoned After Fainting At Music Festival, Starts Wondering If He Should Call Off Wedding</t>
+          <t>31 Clever And Absurd Comics By John Atkinson That Put A Weird Spin On Random Everyday Thoughts</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0011-man-feels-abandoned-after-fainting-at-music-festival-starts-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0011-31-clever-and-absurd-comics-by-john-atkinson-that-put-a-weir.jpg</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>58 Times Kids Were So Betrayed By Their Parents, They Never Saw Them Again</t>
+          <t>This Cartoonist Created 39 Weird, Dark Humor Comics Full Of Bizarre Twists</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0012-58-times-kids-were-so-betrayed-by-their-parents-they-never-s.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0012-this-cartoonist-created-39-weird-dark-humor-comics-full-of-b.jpg</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Childfree Woman’s Response To One Pregnancy Comment Left An Entire Wedding Table Stunned</t>
+          <t>32 Wild And Unsettling Vintage Toy Designs By Shampoooty That Defy Norms</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0013-childfree-womans-response-to-one-pregnancy-comment-left-an-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0013-32-wild-and-unsettling-vintage-toy-designs-by-shampoooty-tha.jpg</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>69 People Who Quit Their Jobs To Travel Share If They Regret It Now</t>
+          <t>The Best 100 Comics By Stephen Beals About Retail, Work Stress, And Customer Interactions (Part 1)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0014-69-people-who-quit-their-jobs-to-travel-share-if-they-regret.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0014-the-best-100-comics-by-stephen-beals-about-retail-work-stres.jpg</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>“Which Ancient Civilization Would You Have Thrived In?”: Find Out In 27 Questions</t>
+          <t>Daily Word Search Game #031 (Jun 18, 2026)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0015-which-ancient-civilization-would-you-have-thrived-in-find-ou.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0015-daily-word-search-game-031-jun-18-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>53 Pieces Of History That Sent People Down A Rabbit Hole</t>
+          <t>33 Wholesome Posts About Men Defining Masculinity In Their Own Way</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0016-53-pieces-of-history-that-sent-people-down-a-rabbit-hole.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0016-33-wholesome-posts-about-men-defining-masculinity-in-their-o.jpg</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>87 Myths About Men And Women That People Refuse To Let Go Of</t>
+          <t>27 Times A Perfectly Normal Person Turned Out To Have A Dark Side</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0017-87-myths-about-men-and-women-that-people-refuse-to-let-go-of.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0017-27-times-a-perfectly-normal-person-turned-out-to-have-a-dark.jpg</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>33 Unbelievably Creepy Things That Happened To People</t>
+          <t>69 “Comments You Can Hear” That Practically Read Themselves Out Loud</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0018-33-unbelievably-creepy-things-that-happened-to-people.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0018-69-comments-you-can-hear-that-practically-read-themselves-ou.jpg</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #093 (Jun 24, 2026)</t>
+          <t>Doctor Exposes Shocking Studies On Women’s Health, And People Are Absolutely Furious</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0019-daily-guess-the-timeline-game-093-jun-24-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0019-doctor-exposes-shocking-studies-on-womens-health-and-people-.jpg</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bombshell Report Reveals Jennifer Aniston And Other A-Listers Involved In Hollywood Voting Scandal</t>
+          <t>This Artist Captures The Chaos, Charm, And Confidence Of Pomeranians In 40 Comics</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0020-bombshell-report-reveals-jennifer-aniston-and-other-a-lister.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0020-this-artist-captures-the-chaos-charm-and-confidence-of-pomer.jpg</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91 Historic Photos That Show How Much These Places Have Changed</t>
+          <t>Daily Guess The Famous Person Game #092 (Jun 18, 2026)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0021-91-historic-photos-that-show-how-much-these-places-have-chan.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0021-daily-guess-the-famous-person-game-092-jun-18-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Woman Gets Engaged, Twin Sister’s First Question Isn’t About The Wedding</t>
+          <t>49 Last Minute Father’s Day Gifts That Are So Good Dad Will Never Know You Ordered Them Yesterday</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0022-woman-gets-engaged-twin-sisters-first-question-isnt-about-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0022-49-last-minute-fathers-day-gifts-that-are-so-good-dad-will-n.jpg</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>57 Internet Posts That Aged Better Than Anyone Could Have Imagined (New Pics)</t>
+          <t>40 Unsettling True Stories From “Oddly Horrifying” That Show How Dark The Real World Can Be (New Pics)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0023-57-internet-posts-that-aged-better-than-anyone-could-have-im.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0023-40-unsettling-true-stories-from-oddly-horrifying-that-show-h.jpg</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>After Years Of Silence, Joe Manganiello Reveals His Life-Threatening Health Battle And Major ‘Amputation’</t>
+          <t>30 Wild Stories Of People Whose Double Lives Eventually Caught Up With Them</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0024-after-years-of-silence-joe-manganiello-reveals-his-life-thre.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0024-30-wild-stories-of-people-whose-double-lives-eventually-caug.jpg</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #039 (Jun 24, 2026)</t>
+          <t>“May God Punish You For How You Treated Me”: 76 Online Reviews That Are Funnier Than They Should Be</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0025-daily-guess-the-country-game-039-jun-24-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0025-may-god-punish-you-for-how-you-treated-me-76-online-reviews-.jpg</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>57 Incredible Photos Shared By The ‘Raw Oceanlife’ Page That Capture The Wild Beauty Of The Deep Blue Sea</t>
+          <t>“What Is The Dumbest Thing You Have Been Told Is Not Manly Or Not Feminine?” (62 Answers)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0026-57-incredible-photos-shared-by-the-raw-oceanlife-page-that-c.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0026-what-is-the-dumbest-thing-you-have-been-told-is-not-manly-or.jpg</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Artist Creates 39 Hilarious Comics About Friendship, Dating, And Everyday Life</t>
+          <t>Guy Dangles Engagement Ring To Get GF To Share Authorship Of Her Book, Won’t Take No For An Answer</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0027-artist-creates-39-hilarious-comics-about-friendship-dating-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0027-guy-dangles-engagement-ring-to-get-gf-to-share-authorship-of.jpg</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30 New “Off The Leash” Comics That Perfectly Capture Life With Dogs</t>
+          <t>Man Walks In On Gym Bros Hooking Up In The Steam Room, Gets Blamed For Ruining Their Alpha Image</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0028-30-new-off-the-leash-comics-that-perfectly-capture-life-with.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0028-man-walks-in-on-gym-bros-hooking-up-in-the-steam-room-gets-b.jpg</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>75 Memes That Perfectly Sum Up The Chaos Of Being Alive Right Now</t>
+          <t>Controlling Parents Hijack Son’s Beach Trip, Call Him Ungrateful When He Cancels The Whole Thing</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0029-75-memes-that-perfectly-sum-up-the-chaos-of-being-alive-righ.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0029-controlling-parents-hijack-sons-beach-trip-call-him-ungratef.jpg</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #037 (Jun 24, 2026)</t>
+          <t>Guy Cheats On Wife With A Coworker, Her Kids Methodically Destroy Everything He Built</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0030-daily-word-search-game-037-jun-24-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0030-guy-cheats-on-wife-with-a-coworker-her-kids-methodically-des.jpg</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>People Photos From The 2025 Chromatic Awards That Capture The Range Of Culture In Our World (35 Pics)</t>
+          <t>Mom Gets Spoiled All Day On Mother’s Day, Still Finds A Reason To Throw A Massive Tantrum</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0031-people-photos-from-the-2025-chromatic-awards-that-capture-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0031-mom-gets-spoiled-all-day-on-mothers-day-still-finds-a-reason.jpg</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rope Jumping Tragedy Continues To Develop As Authorities Arrest Three More Over Disturbing Claims</t>
+          <t>17YO Traumatized With Dad’s Reaction To Her Illness, Ends Up Keeping It A Secret But Drama Ensues</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0032-rope-jumping-tragedy-continues-to-develop-as-authorities-arr.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0032-17yo-traumatized-with-dads-reaction-to-her-illness-ends-up-k.jpg</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Animal Behavior Expert Explains 17 Common Things People Get Wrong About Cats</t>
+          <t>35 Times A Friend Did One Thing So Disturbing It Changed How People Saw Them Forever</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0033-animal-behavior-expert-explains-17-common-things-people-get-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0033-35-times-a-friend-did-one-thing-so-disturbing-it-changed-how.jpg</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>This Illustrator Reimagined Animals And Places As Human Characters In 22 Playful Artworks</t>
+          <t>Guy Controls Stepdaughter With Ridiculous Rules, Cries Foul As She Finally Cuts Ties For Good</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0034-this-illustrator-reimagined-animals-and-places-as-human-char.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0034-guy-controls-stepdaughter-with-ridiculous-rules-cries-foul-a.jpg</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #098 (Jun 24, 2026)</t>
+          <t>Employee Asks For A Raise For Years, Boss Learns How Expensive “No” Can Be</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0035-daily-guess-the-famous-person-game-098-jun-24-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0035-employee-asks-for-a-raise-for-years-boss-learns-how-expensiv.jpg</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #092 (Jun 23, 2026)</t>
+          <t>Daily Guess The Timeline Game #086 (Jun 17, 2026)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0036-daily-guess-the-timeline-game-092-jun-23-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0036-daily-guess-the-timeline-game-086-jun-17-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Woman Who Tattooed Both Her Eyes Reveals 10 Ways The Procedure Changed Her Life For The Worse</t>
+          <t>“Is Your Disney IQ Above Average?”: Prove It By Guessing 16 Characters From Their Eyes</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0037-woman-who-tattooed-both-her-eyes-reveals-10-ways-the-procedu.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-is-your-disney-iq-above-average-prove-it-by-guessing-16-char.jpg</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>“Descending Into The Abyss”: 60 Liminal Spaces So Deeply Unsettling We’re Sorry In Advance</t>
+          <t>Guy Meets The Wife Of His Ex-Wife’s Affair Partner And Realizes Something</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0038-descending-into-the-abyss-60-liminal-spaces-so-deeply-unsett.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0038-guy-meets-the-wife-of-his-ex-wifes-affair-partner-and-realiz.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>38 Clever Comics By This Artist That Joke About Relationships, Technology, And Everyday Anxiety</t>
+          <t>“I Don’t Have A Red Flag”: 27 Questions That Will Probably Prove You Wrong</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0039-38-clever-comics-by-this-artist-that-joke-about-relationship.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0039-i-dont-have-a-red-flag-27-questions-that-will-probably-prove.jpg</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>“Where Have I Seen That Dress?”: 18 Memorable Outfits For You To Match To The TV Show</t>
+          <t>Millionaire Connected To UK Royals Arrested 9 Years After Jogger Caught On Video pushing Woman In Front Of Bus</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0040-where-have-i-seen-that-dress-18-memorable-outfits-for-you-to.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0040-millionaire-connected-to-uk-royals-arrested-9-years-after-jo.jpg</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #038 (Jun 23, 2026)</t>
+          <t>These 109 Bakers Took Dessert Decorating To An Entirely Different Level (New Pics)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0041-daily-guess-the-country-game-038-jun-23-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0041-these-109-bakers-took-dessert-decorating-to-an-entirely-diff.jpg</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>85 Tumblr Posts That Deserve To Stay On The Internet Forever (New Pics)</t>
+          <t>A Lifelong Bond Between Siblings Crumbles When Woman Realizes Brother Kept A Major Secret Only From Her</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0042-85-tumblr-posts-that-deserve-to-stay-on-the-internet-forever.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0042-a-lifelong-bond-between-siblings-crumbles-when-woman-realize.jpg</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A Longtime New Yorker Cartoonist Captures The Strange Logic Of Everyday Life (24 New Pics)</t>
+          <t>Update In Case Of Imprisoned Woman Who Set Her Male Friend On Fire Over ‘Misogynist’ Comment</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0043-a-longtime-new-yorker-cartoonist-captures-the-strange-logic-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0043-update-in-case-of-imprisoned-woman-who-set-her-male-friend-o.jpg</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>If You Can Solve All 14 Of These Two-Clue Riddles, You’re More Knowledgeable Than Most</t>
+          <t>“Overstimulating Americanness”: 79 Parts Of US Culture Tourists Weren’t Ready For</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0044-if-you-can-solve-all-14-of-these-two-clue-riddles-youre-more.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0044-overstimulating-americanness-79-parts-of-us-culture-tourists.jpg</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A Roman Historian Who Called Christianity Evil Accidentally Wrote The Best Proof That Jesus Existed</t>
+          <t>75 Times Urban Planners Failed To Predict What People Want, And It Resulted In ‘Desire Paths’ Around The City (New Pics)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0045-a-roman-historian-who-called-christianity-evil-accidentally-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0045-75-times-urban-planners-failed-to-predict-what-people-want-a.jpg</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>If You’re Feeling Down, Here Are 42 Posts That Are Oddly Wholesome</t>
+          <t>Daily Guess The Country Game #032 (Jun 17, 2026)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0046-if-youre-feeling-down-here-are-42-posts-that-are-oddly-whole.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0046-daily-guess-the-country-game-032-jun-17-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nurses Say These 40 Cases Are The Most Mysterious Things They Saw During Their Career</t>
+          <t>From Public Meltdowns To Strange Confessions, 38 People Share How Their Relationships Ended</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0047-nurses-say-these-40-cases-are-the-most-mysterious-things-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0047-from-public-meltdowns-to-strange-confessions-38-people-share.jpg</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Husband Keeps Saying Wife Has Changed Since Having Kids, She Finally Connects The Dots</t>
+          <t>“I Want People To Feel More Understood”: 30 New Relatable Comics By Krysten Bevilaqua</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0048-husband-keeps-saying-wife-has-changed-since-having-kids-she-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0048-i-want-people-to-feel-more-understood-30-new-relatable-comic.jpg</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #036 (Jun 23, 2026)</t>
+          <t>“Can You Solve Them All?”: 15 Math Puzzles That Are Trickier Than They First Seem</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0049-daily-word-search-game-036-jun-23-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0049-can-you-solve-them-all-15-math-puzzles-that-are-trickier-tha.jpg</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Couple Gets Annoyed That SIL’s Cancer Is Overshadowing Their Wedding, The Truth Is Much Worse</t>
+          <t>31 New Comedic Animal Portraits By Alison Friend That Make Pets Look Like Tiny Eccentric Nobles</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0050-couple-gets-annoyed-that-sils-cancer-is-overshadowing-their-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0050-31-new-comedic-animal-portraits-by-alison-friend-that-make-p.jpg</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Entitled Mom Thinks New Homeowner Owes Her Son An Explanation</t>
+          <t>64 Random Silly Memes That Might Bring A Smile To Anyone Feeling Overwhelmed Today</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0051-entitled-mom-thinks-new-homeowner-owes-her-son-an-explanatio.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0051-64-random-silly-memes-that-might-bring-a-smile-to-anyone-fee.jpg</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>This Artist Illustrates The Struggles Of An Everyday Girl In These 5 New Comics</t>
+          <t>Daily Word Search Game #030 (Jun 17, 2026)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0052-this-artist-illustrates-the-struggles-of-an-everyday-girl-in.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0052-daily-word-search-game-030-jun-17-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A History Researcher Reveals 20 Lost Treasures Worth Billions That Have Never Been Found</t>
+          <t>30 Unfiltered Images That Show Real Life Across The Globe By This Street Photographer (New Pics)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0053-a-history-researcher-reveals-20-lost-treasures-worth-billion.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0053-30-unfiltered-images-that-show-real-life-across-the-globe-by.jpg</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>These Wawawiwa Comics Are Here To Add Some Wholesome Joy To Your Day (73 New Pics)</t>
+          <t>Rather Than Decorating The Body, I Design Tattoos That Work With It (53 Pics)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0054-these-wawawiwa-comics-are-here-to-add-some-wholesome-joy-to-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0054-rather-than-decorating-the-body-i-design-tattoos-that-work-w.jpg</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>These Memes From “Animals Doing Things” Are Cute, Chaotic, And Very Relatable (40 New Pics)</t>
+          <t>103 Tattoo Fails That Are Impossible To Ignore (New Pics)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0055-these-memes-from-animals-doing-things-are-cute-chaotic-and-v.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0055-103-tattoo-fails-that-are-impossible-to-ignore-new-pics.jpg</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>95 Posts That Taught People Something They Never Knew They Needed To Know</t>
+          <t>“It Was A Cult”: 49 Times People Realized That Something Was Very Wrong And They Needed To Leave</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0056-95-posts-that-taught-people-something-they-never-knew-they-n.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0056-it-was-a-cult-49-times-people-realized-that-something-was-ve.jpg</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>54 Hilarious Signs Found In The Wild That Prove Park Rangers Have The Best Sense Of Humor</t>
+          <t>Bride Couldn’t Believe What MIL Did At The Wedding, Neither Could The Guests</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0057-54-hilarious-signs-found-in-the-wild-that-prove-park-rangers.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0057-bride-couldnt-believe-what-mil-did-at-the-wedding-neither-co.jpg</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Parents Think They Can Still Control Their Adult Daughter, Things Don’t Go As Planned</t>
+          <t>82 Incredible Historical Finds That Left People Staring In Disbelief (New Pics)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0058-parents-think-they-can-still-control-their-adult-daughter-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0058-82-incredible-historical-finds-that-left-people-staring-in-d.jpg</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>107 Brutal Roasts The Victims Probably Still Think About</t>
+          <t>Daily Guess The Famous Person Game #091 (Jun 17, 2026)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0059-107-brutal-roasts-the-victims-probably-still-think-about.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0059-daily-guess-the-famous-person-game-091-jun-17-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>“It’s Super Meaningful”: 65 People Share The Stories Behind Their Most Cherished Tattoos</t>
+          <t>56 Women Share The Comments They Received About Their Bodies That They Didn’t See Coming</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0060-its-super-meaningful-65-people-share-the-stories-behind-thei.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0060-56-women-share-the-comments-they-received-about-their-bodies.jpg</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>52 Pics That Prove Slavic People Operate On A Wavelength The Rest Of Us Can’t Access</t>
+          <t>Conservative Law Allows Pharmacists To Deny Service, But One 85-Year-Old’s Epic Response Leaves Them Stunned</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0061-52-pics-that-prove-slavic-people-operate-on-a-wavelength-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0061-conservative-law-allows-pharmacists-to-deny-service-but-one-.jpg</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mom Of Girls Harassed By “Male Karen” In Viral Restroom Video Breaks Silence With Scathing Post Against Dad</t>
+          <t>Exhausted Wife Works Two Jobs While Unemployed Husband Lives In Digital Reality Thinking He’s Productive</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0062-mom-of-girls-harassed-by-male-karen-in-viral-restroom-video-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0062-exhausted-wife-works-two-jobs-while-unemployed-husband-lives.jpg</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>73 Random Facts That Might Make People Go: “Why On Earth Do You Know That?”</t>
+          <t>42 Experiences With The Youngest Generation That Make People Feel The World Is Doomed</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0063-73-random-facts-that-might-make-people-go-why-on-earth-do-yo.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0063-42-experiences-with-the-youngest-generation-that-make-people.jpg</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>49 Things People Said Really Hurt Them Despite Their High Pain Tolerance</t>
+          <t>Dad Spent All His Money On Stepdaughter While Watching Bio Kids Suffer, Son Devastated By The Truth</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0064-49-things-people-said-really-hurt-them-despite-their-high-pa.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0064-dad-spent-all-his-money-on-stepdaughter-while-watching-bio-k.jpg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Woman Confused Why MIL Can’t Wear White To Her Wedding, Groom Makes An Update And Shares What Happened</t>
+          <t>Toxic Boss Forced To Close Business After Insulting Top Performer, Ends Up Having His Clients Stolen</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0065-woman-confused-why-mil-cant-wear-white-to-her-wedding-groom-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0065-toxic-boss-forced-to-close-business-after-insulting-top-perf.jpg</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>This Artist’s Watercolor Cat Paintings Are Full Of Personality And Charm (45 Pics)</t>
+          <t>Delulu Mom Wants A Perfect Blended Family, Throws A Hissy Fit When Kids Reject Her Ideology</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0066-this-artists-watercolor-cat-paintings-are-full-of-personalit.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0066-delulu-mom-wants-a-perfect-blended-family-throws-a-hissy-fit.jpg</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22 Prime Day Deals So Good We Actually Gasped A Little When We Saw The Prices</t>
+          <t>Postpartum Wife’s 1000 Tinder Matches Shock Hubby, But The Truth Shatters Him More</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0067-22-prime-day-deals-so-good-we-actually-gasped-a-little-when-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0067-postpartum-wifes-1000-tinder-matches-shock-hubby-but-the-tru.jpg</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>“Paint The Stairs Pink”: 44 Silly Solutions To Really Serious Issues</t>
+          <t>Woman Can’t Figure Out Why Her Wedding News Falls Flat, Best Friend Knows The Uncomfortable Truth</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0068-paint-the-stairs-pink-44-silly-solutions-to-really-serious-i.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0068-woman-cant-figure-out-why-her-wedding-news-falls-flat-best-f.jpg</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>These 27 General Knowledge Questions Start Easy, And End Surprisingly Hard</t>
+          <t>Family Bows To Demanding MIL’s Every Wish, Woman Becomes The First To Stand Up To Her</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0069-these-27-general-knowledge-questions-start-easy-and-end-surp.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0069-family-bows-to-demanding-mils-every-wish-woman-becomes-the-f.jpg</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #097 (Jun 23, 2026)</t>
+          <t>Unhinged Woman Sparks Drama With Her Racism All Because Her Crush Drew Her Bestie’s Portrait</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0070-daily-guess-the-famous-person-game-097-jun-23-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0070-unhinged-woman-sparks-drama-with-her-racism-all-because-her-.jpg</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Woman Loses It After BF Reveals Stepsis Was His Ex And That He Wants Her As Bridesmaid</t>
+          <t>Cranky Neighbor Sparks Property Feud, Creates Huge Mess For Himself Instead</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0071-woman-loses-it-after-bf-reveals-stepsis-was-his-ex-and-that-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0071-cranky-neighbor-sparks-property-feud-creates-huge-mess-for-h.jpg</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Student Baffled Over Her Parents’ Unexpected Hostility As They Give Her Room To Jobless Brother</t>
+          <t>“Your Body Will Simply Give Up”: 38 Human Body Facts That Might Make You Scared To Be Alive</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0072-student-baffled-over-her-parents-unexpected-hostility-as-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0072-your-body-will-simply-give-up-38-human-body-facts-that-might.jpg</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dad And His Friend Joke About Daughters Being Difficult, One Remark From His Teen Changes The Mood</t>
+          <t>Daily Guess The Timeline Game #085 (Jun 16, 2026)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0073-dad-and-his-friend-joke-about-daughters-being-difficult-one-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0073-daily-guess-the-timeline-game-085-jun-16-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Woman Disinvited From Hubs’ Bestie’s Destination Wedding Last-Minute, Hubs Sees Red And RSVPs No</t>
+          <t>Mom Thinks Everyone Else Is Overreacting To Daughter’s Behavior, Commenters Disagree</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0074-woman-disinvited-from-hubs-besties-destination-wedding-last-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0074-mom-thinks-everyone-else-is-overreacting-to-daughters-behavi.jpg</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wife Asks To Hang Out With Guy She Opened The Marriage For, Her Husband Has Finally Had Enough</t>
+          <t>“She Refused To Speak To The Staff”: 35 Celebrity Encounters That Were A Lot To Witness</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0075-wife-asks-to-hang-out-with-guy-she-opened-the-marriage-for-h.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0075-she-refused-to-speak-to-the-staff-35-celebrity-encounters-th.jpg</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Manipulative Mom Tried To Sneak Her Son Onto A Vacation, It Blows Up Hard On Her Face</t>
+          <t>Woman Survives A Workplace Emergency, Then Finds Herself In Even More Trouble</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0076-manipulative-mom-tried-to-sneak-her-son-onto-a-vacation-it-b.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0076-woman-survives-a-workplace-emergency-then-finds-herself-in-e.jpg</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Birthday Woman Chooses Thai Restaurant For Dinner, Then Gets Cut Out Of Her Own Party</t>
+          <t>19 Celebrities Showed Up To Watch UFC At The White House, And The Guest List Is A Lot To Process</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0077-birthday-woman-chooses-thai-restaurant-for-dinner-then-gets-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0077-19-celebrities-showed-up-to-watch-ufc-at-the-white-house-and.jpg</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Toxic Friend Frames Woman And Steals Her Blind Date, Gets What She Deserved The Very Next Day</t>
+          <t>Passenger Tormented By Racist Woman On Flight Gets An Upgrade, She Gets Shut Down By The Crew</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0078-toxic-friend-frames-woman-and-steals-her-blind-date-gets-wha.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0078-passenger-tormented-by-racist-woman-on-flight-gets-an-upgrad.jpg</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #091 (Jun 22, 2026)</t>
+          <t>21 Mind-Bending Dilemmas That’ll Challenge Your Morals: Vote Now &amp; See Where You Stand</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0079-daily-guess-the-timeline-game-091-jun-22-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0079-21-mind-bending-dilemmas-thatll-challenge-your-morals-vote-n.jpg</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>57 Times People Laughed Without Context And Immediately Regretted It</t>
+          <t>53 Toxic Friends Who Hurt People In Ways They Never Saw Coming</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0080-57-times-people-laughed-without-context-and-immediately-regr.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0080-53-toxic-friends-who-hurt-people-in-ways-they-never-saw-comi.jpg</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>53 Airport Photos So Ridiculous They Might Make Travelers Miss Their Flights From Laughing</t>
+          <t>Children Of Karen Parents Are Sharing Their Wildest Stories, And They’re Brutal</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0081-53-airport-photos-so-ridiculous-they-might-make-travelers-mi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0081-children-of-karen-parents-are-sharing-their-wildest-stories-.jpg</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15 Modern Adulting Questions Every Grown-Up Should Be Able To Answer – Test Yourself</t>
+          <t>Trauma Bonding: Signs, Stages, and How to Break Free</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0082-15-modern-adulting-questions-every-grown-up-should-be-able-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0082-trauma-bonding-signs-stages-and-how-to-break-free.jpg</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #037 (Jun 22, 2026)</t>
+          <t>Narcissistic Guy Refuses To Pay Spousal Support And Takes Ex To Court, Ends Up Paying With 401k</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0083-daily-guess-the-country-game-037-jun-22-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0083-narcissistic-guy-refuses-to-pay-spousal-support-and-takes-ex.jpg</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>65 New Sarcasm-Filled Comics By The Artist Steve Nelson</t>
+          <t>I Illustrate The Hilarious Reality Of A Rescue Dog And A Cat Living Together (25 New Comics)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0084-65-new-sarcasm-filled-comics-by-the-artist-steve-nelson.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0084-i-illustrate-the-hilarious-reality-of-a-rescue-dog-and-a-cat.jpg</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>64 Times People Asked Their Partner To Stop Doing Something Gross, And Failed</t>
+          <t>Daily Guess The Country Game #031 (Jun 16, 2026)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0085-64-times-people-asked-their-partner-to-stop-doing-something-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0085-daily-guess-the-country-game-031-jun-16-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Guy Has Suspicions Over Daughter Not Being His, Turns Out It’s Way Worse Than He Could Have Guessed</t>
+          <t>This Photographer Captured 42 Dreamlike Images Of Antarctica</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0086-guy-has-suspicions-over-daughter-not-being-his-turns-out-its.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0086-this-photographer-captured-42-dreamlike-images-of-antarctica.jpg</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>74 Electronics Fails So Bad They Basically Wrote Their Own Eulogy</t>
+          <t>39 Captivating Travel Photos From The 2025 Chromatic Awards That Show How Diverse The World Is</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0087-74-electronics-fails-so-bad-they-basically-wrote-their-own-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0087-39-captivating-travel-photos-from-the-2025-chromatic-awards-.jpg</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18 Human Habits That Confuse Dogs The Most, According To An Animal Behaviorist</t>
+          <t>“Can You Still Solve Basic Equations?”: Ace This 20-Question Math Quiz And Reveal The Truth</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0088-18-human-habits-that-confuse-dogs-the-most-according-to-an-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0088-can-you-still-solve-basic-equations-ace-this-20-question-mat.jpg</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Name All 22 World Capitals From Two Clues Each – Prove Your Geography Knowledge</t>
+          <t>This Page Shared 26 Heartwarming Animal Moments From Around The World (New Pics)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0089-name-all-22-world-capitals-from-two-clues-each-prove-your-ge.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0089-this-page-shared-26-heartwarming-animal-moments-from-around-.jpg</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>63 Absolutely Atrocious Clothing Design Fails That Might Make You Giggle</t>
+          <t>25 Remarkable Dog Rescue Transformations Shared By NIRA That Show The Power Of A Second Chance</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0090-63-absolutely-atrocious-clothing-design-fails-that-might-mak.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0090-25-remarkable-dog-rescue-transformations-shared-by-nira-that.jpg</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Artist Shares 57 New Comics About Ferrets, Pets, And Everyday Absurdities</t>
+          <t>Daily Word Search Game #029 (Jun 16, 2026)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0091-artist-shares-57-new-comics-about-ferrets-pets-and-everyday-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0091-daily-word-search-game-029-jun-16-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1830,8 +1830,16 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>23 Hilarious Father’s Day Gifts For The Dad Whose Sense Of Humor Is The Best Thing He Passed Down</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0092-23-hilarious-fathers-day-gifts-for-the-dad-whose-sense-of-hu.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1839,12 +1847,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #035 (Jun 22, 2026)</t>
+          <t>30 New Comics By Brian Gordon Showcasing The Funny Side Of Parenting</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0093-daily-word-search-game-035-jun-22-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0093-30-new-comics-by-brian-gordon-showcasing-the-funny-side-of-p.jpg</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1862,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>“Bride Of Chucky”: Evil MIL Takes Twisted Joke A Step Too Far, Leaving Wedding Guests Horrified</t>
+          <t>Emily Ratajkowski Faces Backlash Over Essay About Single Motherhood Accompanied By Bizarre Breastfeeding Photo</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0094-bride-of-chucky-evil-mil-takes-twisted-joke-a-step-too-far-l.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0094-emily-ratajkowski-faces-backlash-over-essay-about-single-mot.jpg</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1877,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Woman Loses Husband And Best Friend To An Affair, Gets The Last Laugh Years Later</t>
+          <t>67 Brutally Honest Posts From Millennials On Social Media (New Pics)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0095-woman-loses-husband-and-best-friend-to-an-affair-gets-the-la.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0095-67-brutally-honest-posts-from-millennials-on-social-media-ne.jpg</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1892,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>84 Tragic Hair Accidents That Should Never Have Seen The Light Of Day (New Pics)</t>
+          <t>63 Awkward Texts That Are So Bad It’s Funny (New Pics)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0096-84-tragic-hair-accidents-that-should-never-have-seen-the-lig.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0096-63-awkward-texts-that-are-so-bad-its-funny-new-pics.jpg</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1907,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>35 Cases So Bizarre People Still Argue About Them Today</t>
+          <t>“Unsure About Dinosaurs”: 50 People Who Dated Morons Reveal Their Dumbest Beliefs</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0097-35-cases-so-bizarre-people-still-argue-about-them-today.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0097-unsure-about-dinosaurs-50-people-who-dated-morons-reveal-the.jpg</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1922,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Guy Tries To Control What Neighbor Wears Outside, Doesn’t Get The Response He Wanted</t>
+          <t>This Instagram Account Shares Hilarious Design Fails, Here Are 91 Of The Best (New Pics)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0098-guy-tries-to-control-what-neighbor-wears-outside-doesnt-get-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0098-this-instagram-account-shares-hilarious-design-fails-here-ar.jpg</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1937,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>“Wake My Son Up For School”: 65 Entitled Messages That Left Teachers Speechless</t>
+          <t>Spiteful Grandma Spills Decades-Old Secret In Most Brutal Way Possible And Faces Immediate Family Exile</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0099-wake-my-son-up-for-school-65-entitled-messages-that-left-tea.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0099-spiteful-grandma-spills-decades-old-secret-in-most-brutal-wa.jpg</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1952,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #096 (Jun 22, 2026)</t>
+          <t>This Page Shared 65 Irresistible Pics Of Baby Animals And Their Moms</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0100-daily-guess-the-famous-person-game-096-jun-22-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0100-this-page-shared-65-irresistible-pics-of-baby-animals-and-th.jpg</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1967,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>56 Secrets People In Long-Term Relationships Are Keeping From Their Partners</t>
+          <t>Daily Guess The Famous Person Game #090 (Jun 16, 2026)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0101-56-secrets-people-in-long-term-relationships-are-keeping-fro.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0101-daily-guess-the-famous-person-game-090-jun-16-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1982,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>“How Academic Are You?”: 25 Smart English Words That Only Advanced Speakers Know</t>
+          <t>We Prepared 26 Pop Culture Questions From A To Z – Anything Above 22 Is An Excellent Score</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0102-how-academic-are-you-25-smart-english-words-that-only-advanc.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0102-we-prepared-26-pop-culture-questions-from-a-to-z-anything-ab.jpg</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1997,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16 Prime Day Deals That Started Early And Are Honestly Too Good To Just Scroll Past</t>
+          <t>30 Times Folks Online Were Disturbed By The People Their Friends Were Dating</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0103-16-prime-day-deals-that-started-early-and-are-honestly-too-g.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0103-30-times-folks-online-were-disturbed-by-the-people-their-fri.jpg</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2012,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bride Lies About Food At Her Wedding To Prove A Point But Only Gets Coworker’s Child Hospitalized</t>
+          <t>71 Times People Thought They Took Normal Photos Until They Turned Into Hilarious ‘When You See It’ Moments (New Pics)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0104-bride-lies-about-food-at-her-wedding-to-prove-a-point-but-on.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0104-71-times-people-thought-they-took-normal-photos-until-they-t.jpg</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2027,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>71 Posts That Gave People An Unexpected Existential Crisis About Their Age (New Pics)</t>
+          <t>19YO Gets Dismissed By Know-It-All Nurse, Returns A Week Later With A Huge Infection Instead</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0105-71-posts-that-gave-people-an-unexpected-existential-crisis-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0105-19yo-gets-dismissed-by-know-it-all-nurse-returns-a-week-late.jpg</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2042,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>“It Didn’t Work”: 43 Stories About What It’s Really Like To Live In A Polygamist Household</t>
+          <t>Aunt Tired Of Playing Emergency Contact For 5YO In Constant Trouble, Demands Parents Face Reality</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0106-it-didnt-work-43-stories-about-what-its-really-like-to-live-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0106-aunt-tired-of-playing-emergency-contact-for-5yo-in-constant-.jpg</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2057,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>People Are Sharing The Most Infuriating But Also Hilarious Food Delivery Driver Fails</t>
+          <t>VIP Passenger Picks Drinking Over Taking Care Of Her Kids, Pilot Ends Up Teaching Her A Lesson</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0107-people-are-sharing-the-most-infuriating-but-also-hilarious-f.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0107-vip-passenger-picks-drinking-over-taking-care-of-her-kids-pi.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2072,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>“Am I The Jerk For Telling My Dad I Don’t Care About The Kids He Replaced Me With?”</t>
+          <t>Couple Are Warned About Nightmare Neighbor, Move In Across The Road Anyway, Regret It Immediately</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0108-am-i-the-jerk-for-telling-my-dad-i-dont-care-about-the-kids-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0108-couple-are-warned-about-nightmare-neighbor-move-in-across-th.jpg</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2087,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Family Tries To Challenge Grandma’s Will At Her Funeral, One Man’s Speech Changes Everything</t>
+          <t>Vicious Aunt Berates “Unladylike” Niece, Doesn’t Realize She’s Saying Goodbye To Her Own Cash Flow</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0109-family-tries-to-challenge-grandmas-will-at-her-funeral-one-m.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0109-vicious-aunt-berates-unladylike-niece-doesnt-realize-shes-sa.jpg</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2102,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Parents Laugh When Son Says They Always Choose Adopted Kid, He Returns The Favor By Ditching Them</t>
+          <t>Mom Lets Stepkids Make Daughter Miserable For Years, Suddenly Wants A Second Chance When She’s Gone</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0110-parents-laugh-when-son-says-they-always-choose-adopted-kid-h.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0110-mom-lets-stepkids-make-daughter-miserable-for-years-suddenly.jpg</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2117,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Attention-Hungry Blogger Exposes Her Family For Clicks, It Blows Up In Her Face</t>
+          <t>49 People With Jobs So Strange Most People Don’t Know They Exist</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0111-attention-hungry-blogger-exposes-her-family-for-clicks-it-bl.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0111-49-people-with-jobs-so-strange-most-people-dont-know-they-ex.jpg</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2132,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>35 Celebrity Scandals That Were So Ridiculous That We’re Still Shocked They Even Happened</t>
+          <t>73 Cursed Images From This Weird Corner Of The Internet (New Pics)</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0112-35-celebrity-scandals-that-were-so-ridiculous-that-were-stil.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0112-73-cursed-images-from-this-weird-corner-of-the-internet-new-.jpg</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2147,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Woman Watches Her Sisterly Bond With Adopted Sis Crumble After Disturbing Wedding Debacle</t>
+          <t>Barron Trump’s UFC Appearance Fuels Concern And Wild Speculation About His Changed Look: “Absolutely Miserable”</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0113-woman-watches-her-sisterly-bond-with-adopted-sis-crumble-aft.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0113-barron-trumps-ufc-appearance-fuels-concern-and-wild-speculat.jpg</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2162,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19 World Cup Stars So Handsome, Fans Can’t Stop Talking About Them</t>
+          <t>50 Funny Cat Memes That Prove Life Is Better When Cats Are Being Weird</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0114-19-world-cup-stars-so-handsome-fans-cant-stop-talking-about-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0114-50-funny-cat-memes-that-prove-life-is-better-when-cats-are-b.jpg</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2177,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #090 (Jun 21, 2026)</t>
+          <t>“Never Expected Me To Turn Her Own Logic Against Her”: Woman Shocks MIL With A Savage Comeback</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0115-daily-guess-the-timeline-game-090-jun-21-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0115-never-expected-me-to-turn-her-own-logic-against-her-woman-sh.jpg</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2192,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>This Scottish X Account Went Viral For Explaining US Slang, Here Are Its 13 Best Posts</t>
+          <t>“If Your Arm Is Gone, It’s A Jaguar”: 73 Animal Facts That Sent Us Down A Rabbit Hole For Hours</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0116-this-scottish-x-account-went-viral-for-explaining-us-slang-h.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0116-if-your-arm-is-gone-its-a-jaguar-73-animal-facts-that-sent-u.jpg</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2207,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>97 “Epic Top Comments” That Are Way More Entertaining Than The Posts They’re On</t>
+          <t>‘Karen’ Proves That Some Parents Need To Snap Back To Reality After She Attacks Disabled Person</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0117-97-epic-top-comments-that-are-way-more-entertaining-than-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0117-karen-proves-that-some-parents-need-to-snap-back-to-reality-.jpg</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2222,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>These 53 Memes Are So Funny They Might Make You Question Your Sanity In The Best Way</t>
+          <t>Daily Guess The Timeline Game #084 (Jun 15, 2026)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0118-these-53-memes-are-so-funny-they-might-make-you-question-you.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0118-daily-guess-the-timeline-game-084-jun-15-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2237,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>“Ancient Macedonian Gold”: 71 Authentic Historical Finds That Might Feel Like Time Travel</t>
+          <t>Woman Shocked That She Might Be “Stealing Friend’s Boyfriend,” The Truth Is More Bizarre Than She Expected</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0119-ancient-macedonian-gold-71-authentic-historical-finds-that-m.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0119-woman-shocked-that-she-might-be-stealing-friends-boyfriend-t.jpg</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2252,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>62 Hilarious Dads Who Were Clearly Born For The Role (New Pics)</t>
+          <t>33 Folks Who Believed Their Friends Were Just “Nice Peeps,” Until Some Discovery Proved The Opposite</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0120-62-hilarious-dads-who-were-clearly-born-for-the-role-new-pic.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0120-33-folks-who-believed-their-friends-were-just-nice-peeps-unt.jpg</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2267,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>77 Cringy And Sad Moments That Will Forever Live As Screenshots On The Internet</t>
+          <t>“Never Came Back To School”: 51 Times The Class Clown Took It Too Far And Faced The Consequences</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0121-77-cringy-and-sad-moments-that-will-forever-live-as-screensh.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0121-never-came-back-to-school-51-times-the-class-clown-took-it-t.jpg</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2282,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>“It Breaks My Heart”: 32 Popular Kids Who Threw Everything Away</t>
+          <t>Only True Music Fans Can Name All 25 Iconic Titles From A Blurry Image</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0122-it-breaks-my-heart-32-popular-kids-who-threw-everything-away.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0122-only-true-music-fans-can-name-all-25-iconic-titles-from-a-bl.jpg</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2297,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>69 Coincidences So Crazy People Still Can’t Wrap Their Heads Around Them</t>
+          <t>We Highly Doubt You Can Beat The Average U.S. Student – Prove Us Wrong In 18 Questions</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0123-69-coincidences-so-crazy-people-still-cant-wrap-their-heads-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0123-we-highly-doubt-you-can-beat-the-average-us-student-prove-us.jpg</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2312,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>75 Creepy Facts And Horror Stories People Wish They Never Learned</t>
+          <t>Woman Finds Out She’s No Longer Invited To Friend’s Wedding, Karma Hits Right Before The Big Day</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0124-75-creepy-facts-and-horror-stories-people-wish-they-never-le.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0124-woman-finds-out-shes-no-longer-invited-to-friends-wedding-ka.jpg</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2327,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>24 Wholesome Posts From The “One Night I Was Bored In Bed” Trend</t>
+          <t>57 Hilariously Random Screenshots That Were Too Funny Not To Share (New Pics)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0125-24-wholesome-posts-from-the-one-night-i-was-bored-in-bed-tre.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0125-57-hilariously-random-screenshots-that-were-too-funny-not-to.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2342,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>“Can You Actually Decide?”: Vote On 17 ‘Would You Rather’ Questions From Films, TV &amp; Books</t>
+          <t>“Is It Tokyo Or Seoul?”: Challenge Your Memory Of The Capitals With 18 Borderless Maps</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0126-can-you-actually-decide-vote-on-17-would-you-rather-question.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0126-is-it-tokyo-or-seoul-challenge-your-memory-of-the-capitals-w.jpg</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2357,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Man Is So Glad He’s Escaping Controlling Fiancée After Finally Checking Their Joint Bank Account</t>
+          <t>Daily Guess The Country Game #030 (Jun 15, 2026)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0127-man-is-so-glad-hes-escaping-controlling-fiancee-after-finall.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0127-daily-guess-the-country-game-030-jun-15-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2364,12 +2372,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #036 (Jun 21, 2026)</t>
+          <t>If You Like Dry Humor, Here Are 58 New One-Panel Comics By Graham Annable To Enjoy</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0128-daily-guess-the-country-game-036-jun-21-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0128-if-you-like-dry-humor-here-are-58-new-one-panel-comics-by-gr.jpg</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2387,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #034 (Jun 21, 2026)</t>
+          <t>43 Underwater Oil Paintings By This Artist, So Beautiful They Feel Like Memories In Motion</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0129-daily-word-search-game-034-jun-21-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0129-43-underwater-oil-paintings-by-this-artist-so-beautiful-they.jpg</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2402,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #095 (Jun 21, 2026)</t>
+          <t>Daily Word Search Game #028 (Jun 15, 2026)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0130-daily-guess-the-famous-person-game-095-jun-21-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0130-daily-word-search-game-028-jun-15-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2417,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #089 (Jun 20, 2026)</t>
+          <t>‘House Of The Dragon’ Season 3 Cast Guide: Every New and Returning Character</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0131-daily-guess-the-timeline-game-089-jun-20-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0131-house-of-the-dragon-season-3-cast-guide-every-new-and-return.jpg</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2432,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>If You Need To Take A Mental Break, These 55 Posts Should Help You Decompress Like A Hot Bath</t>
+          <t>55 Memes Shared By The ‘Ancient Cringe’ Page That Turn Historical Art Into Relatable Comedy</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0132-if-you-need-to-take-a-mental-break-these-55-posts-should-hel.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0132-55-memes-shared-by-the-ancient-cringe-page-that-turn-histori.jpg</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2447,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>“There Was No Grass In Dinosaur Times”: 52 Facts That You Might Not Believe Are Actually True</t>
+          <t>30 Futuristic Chrome Tattoos By This Artist That Look Like They Were Imported From The Future</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0133-there-was-no-grass-in-dinosaur-times-52-facts-that-you-might.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0133-30-futuristic-chrome-tattoos-by-this-artist-that-look-like-t.jpg</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2462,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>56 ER Patients Share The Mistakes That Sent Them To The Hospital</t>
+          <t>Daily Guess The Famous Person Game #089 (Jun 15, 2026)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0134-56-er-patients-share-the-mistakes-that-sent-them-to-the-hosp.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0134-daily-guess-the-famous-person-game-089-jun-15-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2477,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>“Future Tech”: 33 Things People Are Working On Now That Might Change Everything</t>
+          <t>“What Is Something That Is Highly Likely To Happen In The Next 10 Years That Everyone Is Completely Ignoring?” (67 Answers)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0135-future-tech-33-things-people-are-working-on-now-that-might-c.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0135-what-is-something-that-is-highly-likely-to-happen-in-the-nex.jpg</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2492,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>71 History Posts That Sent People Down Unexpected Rabbit Holes</t>
+          <t>We All Make Mistakes, But These 60 Huge Fails Hurt To Laugh At (New Pics)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0136-71-history-posts-that-sent-people-down-unexpected-rabbit-hol.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0136-we-all-make-mistakes-but-these-60-huge-fails-hurt-to-laugh-a.jpg</t>
         </is>
       </c>
     </row>
@@ -2499,12 +2507,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>The Office Struggle Is Real And People Cope By Creating These 77 Hilarious Memes (New Pics)</t>
+          <t>Regretful Husband Deserts His Marriage For A Younger Fantasy, And Now He Can’t Handle The Reality</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0137-the-office-struggle-is-real-and-people-cope-by-creating-thes.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0137-regretful-husband-deserts-his-marriage-for-a-younger-fantasy.jpg</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2522,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>97 Amazing Facts About Our World To Keep You Busy For A Few Minutes</t>
+          <t>New Mom Shocked After Half-Sis Who Struggles With Infertility Said Newborn Was Hers</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0138-97-amazing-facts-about-our-world-to-keep-you-busy-for-a-few-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0138-new-mom-shocked-after-half-sis-who-struggles-with-infertilit.jpg</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2537,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Thousands Of People Love This Page’s Random Sense Of Humor, Here Are 67 Of Its Best Posts</t>
+          <t>20 Harsh Reality Checks From The “Awful Everything” Group That Might Change Your View On Things (New Pics)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0139-thousands-of-people-love-this-pages-random-sense-of-humor-he.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0139-20-harsh-reality-checks-from-the-awful-everything-group-that.jpg</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2552,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>56 Of The Funniest Pop Culture Posts You Can Pass Around For Instant Good Vibes</t>
+          <t>41 Satisfying Petty Revenge Stories Where Cheaters Got What They Deserved</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0140-56-of-the-funniest-pop-culture-posts-you-can-pass-around-for.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0140-41-satisfying-petty-revenge-stories-where-cheaters-got-what-.jpg</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2567,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Couple Has To Change Locks Over MIL’s Behavior, She Refuses To Back Down</t>
+          <t>“AITA For Telling My Family The Real Reason My Mother And I Are Not Attending My Sister’s Wedding?”</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0141-couple-has-to-change-locks-over-mils-behavior-she-refuses-to.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0141-aita-for-telling-my-family-the-real-reason-my-mother-and-i-a.jpg</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2582,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Wife Learns Husband Orchestrated Their Relationship After Shocking Discovery</t>
+          <t>Gossip-Hungry MIL Snoops Through Confidential Files, Learns Attorney DIL Takes Privacy Seriously</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0142-wife-learns-husband-orchestrated-their-relationship-after-sh.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0142-gossip-hungry-mil-snoops-through-confidential-files-learns-a.jpg</t>
         </is>
       </c>
     </row>
@@ -2589,12 +2597,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MIL Wears White To Wedding, Bride Decides To Make Her The Center Of Attention</t>
+          <t>Sister Assumes She Is Getting Pregnant Teen’s Baby Without Asking, Loses It When The Answer Is No</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0143-mil-wears-white-to-wedding-bride-decides-to-make-her-the-cen.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0143-sister-assumes-she-is-getting-pregnant-teens-baby-without-as.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2612,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Boyfriend Says Woman Isn’t Worth It Anymore Just Because She Made Her Boundaries Clear</t>
+          <t>Wife Spends Hours Dealing With Drunk Hubby’s Mess, Then Security Footage Changes Everything</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0144-boyfriend-says-woman-isnt-worth-it-anymore-just-because-she-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0144-wife-spends-hours-dealing-with-drunk-hubbys-mess-then-securi.jpg</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2627,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The Way You Handle Loneliness Says More About You Than You’d Think – Find Out In 27 Questions</t>
+          <t>Woman Tries To Make Sis Feel Bad About Her Past Drinking Problems, Sis Gives Her A Reality Check</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0145-the-way-you-handle-loneliness-says-more-about-you-than-youd-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0145-woman-tries-to-make-sis-feel-bad-about-her-past-drinking-pro.jpg</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2642,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #035 (Jun 20, 2026)</t>
+          <t>Daily Guess The Timeline Game #083 (Jun 14, 2026)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0146-daily-guess-the-country-game-035-jun-20-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0146-daily-guess-the-timeline-game-083-jun-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2657,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #033 (Jun 20, 2026)</t>
+          <t>30 Father’s Day Gifts That Went Completely Off Script And Are Honestly So Much Better For It</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0147-daily-word-search-game-033-jun-20-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0147-30-fathers-day-gifts-that-went-completely-off-script-and-are.jpg</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2672,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #094 (Jun 20, 2026)</t>
+          <t>75 Ironic Posts That Might Make You Chuckle</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0148-daily-guess-the-famous-person-game-094-jun-20-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0148-75-ironic-posts-that-might-make-you-chuckle.jpg</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2687,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Experts Solve Botticelli’s Birth Of Venus Side‑Eye Mystery, And The Reason Is Devastating</t>
+          <t>85 Randomly Funny Memes You Probably Haven’t Seen Before</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0149-experts-solve-botticellis-birth-of-venus-sideeye-mystery-and.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0149-85-randomly-funny-memes-you-probably-havent-seen-before.jpg</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2702,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #088 (Jun 19, 2026)</t>
+          <t>54 Public Monuments That Became Famous For All The Wrong Reasons</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0150-daily-guess-the-timeline-game-088-jun-19-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0150-54-public-monuments-that-became-famous-for-all-the-wrong-rea.jpg</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2717,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>‘Pirates Of The Caribbean’ Made Keira Knightley A Star At 17, Says The Price Was Years Of Therapy</t>
+          <t>81 People Share Photos That Are Almost Too Perfect To Be Real</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0151-pirates-of-the-caribbean-made-keira-knightley-a-star-at-17-s.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0151-81-people-share-photos-that-are-almost-too-perfect-to-be-rea.jpg</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2732,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Why Tech Billionaires No Longer Want Flight Attendants On Their Private Jets</t>
+          <t>“Here To Explain Everything”: 92 Facts And Stories You Might Not Have Heard Of Before</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0152-why-tech-billionaires-no-longer-want-flight-attendants-on-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0152-here-to-explain-everything-92-facts-and-stories-you-might-no.jpg</t>
         </is>
       </c>
     </row>
@@ -2739,12 +2747,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Guy Realizes Why Every Vacation Feels More Like Work Than A Holiday</t>
+          <t>41 Misconceptions And Outdated Beliefs People Proudly Corrected</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0153-guy-realizes-why-every-vacation-feels-more-like-work-than-a-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0153-41-misconceptions-and-outdated-beliefs-people-proudly-correc.jpg</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2762,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Wife’s Suggestion Said In Anger Makes Husband Realize He Loves A Tombstone Too Much</t>
+          <t>85 Feminist Posts That Say The Quiet Part Out Loud</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0154-wifes-suggestion-said-in-anger-makes-husband-realize-he-love.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0154-85-feminist-posts-that-say-the-quiet-part-out-loud.jpg</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2777,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>50 Unhinged Screenshots That Accurately Sum Up Online Dating These Days</t>
+          <t>“Why Aren’t Girls Into Me?”: 50 Real Reasons These Incels Are ‘Forever Alone,’ According To Their Friends</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0155-50-unhinged-screenshots-that-accurately-sum-up-online-dating.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0155-why-arent-girls-into-me-50-real-reasons-these-incels-are-for.jpg</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2792,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Biological Parents Of Baby Born To Different Couple Thanks To IVF-Embryo Mix-Up Lose Custody</t>
+          <t>39 Things Americans Barely Notice That Stand Out To Foreign Visitors</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0156-biological-parents-of-baby-born-to-different-couple-thanks-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0156-39-things-americans-barely-notice-that-stand-out-to-foreign-.jpg</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2807,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>79 Houses So Weird People Couldn’t Believe They Were Actually For Sale</t>
+          <t>“Sickening”: 47 Times Women Deeply Regretted Looking Through Their Partner’s Phone</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0157-79-houses-so-weird-people-couldnt-believe-they-were-actually.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0157-sickening-47-times-women-deeply-regretted-looking-through-th.jpg</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2822,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ex-Girlfriend Assumes Her Former Partner Will Help Her Out, Doesn’t Get The Answer She Wanted</t>
+          <t>Woman Is Asked To Help The Sister Who Slept With Her Boyfriend, Family Drama Follows</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0158-ex-girlfriend-assumes-her-former-partner-will-help-her-out-d.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0158-woman-is-asked-to-help-the-sister-who-slept-with-her-boyfrie.jpg</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2837,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>47 People Share The Spiciest And Most Shocking Secrets From Their Jobs</t>
+          <t>“My Girlfriend Broke Her Back. Her Parents’ Response Shocked Me”</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0159-47-people-share-the-spiciest-and-most-shocking-secrets-from-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0159-my-girlfriend-broke-her-back-her-parents-response-shocked-me.jpg</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2852,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>63 Funny And Cute Cat Photos That Might Make You Smile Today (New Pics)</t>
+          <t>Your Social Battery Has A Limit – These 27 Questions Reveal Exactly Where It Is</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0160-63-funny-and-cute-cat-photos-that-might-make-you-smile-today.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0160-your-social-battery-has-a-limit-these-27-questions-reveal-ex.jpg</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2867,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Family Conflict Resolution: 5 Steps to De-escalate Tension at Home</t>
+          <t>Daily Guess The Country Game #029 (Jun 14, 2026)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0161-family-conflict-resolution-5-steps-to-de-escalate-tension-at.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0161-daily-guess-the-country-game-029-jun-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2882,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>105 Times People Hit The Jackpot While Dumpster Diving (New Pics)</t>
+          <t>Daily Word Search Game #027 (Jun 14, 2026)</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0162-105-times-people-hit-the-jackpot-while-dumpster-diving-new-p.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0162-daily-word-search-game-027-jun-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2897,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #034 (Jun 19, 2026)</t>
+          <t>Daily Guess The Famous Person Game #088 (Jun 14, 2026)</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0163-daily-guess-the-country-game-034-jun-19-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0163-daily-guess-the-famous-person-game-088-jun-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2912,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>15 New Comics By Jordan Bolton That Turn Small Encounters Into Heartbreaking Stories</t>
+          <t>Daily Guess The Timeline Game #082 (Jun 13, 2026)</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0164-15-new-comics-by-jordan-bolton-that-turn-small-encounters-in.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0164-daily-guess-the-timeline-game-082-jun-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2919,12 +2927,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Only High IQs Can Beat All 26 Hard General Knowledge Questions – Prove You’re One</t>
+          <t>For Decades, Wives Paid A Mysterious Woman To Fix Their Marriage—Until A Guilt-Ridden Client Told Police All</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0165-only-high-iqs-can-beat-all-26-hard-general-knowledge-questio.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0165-for-decades-wives-paid-a-mysterious-woman-to-fix-their-marri.jpg</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2942,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Through Her Beautiful Driftwood Sculptures, This Artist Seeks To Highlight The Unity Of Human Beings With Nature (28 New Pics)</t>
+          <t>81 Designs So Bad That They Deserve To Be Named And Shamed Online (New Pics)</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0166-through-her-beautiful-driftwood-sculptures-this-artist-seeks.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0166-81-designs-so-bad-that-they-deserve-to-be-named-and-shamed-o.jpg</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2957,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>20 Children’s Drawings Turned Into Handcrafted Enamel Jewelry By Minttnim</t>
+          <t>67 Wholesome Internet Finds That Might Restore Your Faith In Humanity (New Pics)</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0167-20-childrens-drawings-turned-into-handcrafted-enamel-jewelry.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0167-67-wholesome-internet-finds-that-might-restore-your-faith-in.jpg</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2972,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>This Tattoo Artist Was Given A Once-In-A-Lifetime Opportunity At Space Center Houston</t>
+          <t>Someone Asked For Wholesome Pics Of World Leaders, 35 People Share Their Favorites</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0168-this-tattoo-artist-was-given-a-once-in-a-lifetime-opportunit.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0168-someone-asked-for-wholesome-pics-of-world-leaders-35-people-.jpg</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2987,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>‘Best Bird Shots’ 80 Amazing Photos Showing The Beauty Of Wildlife In Detail</t>
+          <t>‘The Weird Unknown’: 79 Creepy, Weird, And Intriguing Facts About The Ocean (New Pics)</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0169-best-bird-shots-80-amazing-photos-showing-the-beauty-of-wild.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0169-the-weird-unknown-79-creepy-weird-and-intriguing-facts-about.jpg</t>
         </is>
       </c>
     </row>
@@ -2994,12 +3002,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>If You Can Name All 25 Characters From These Silhouettes, Your Movie Knowledge Is Next Level</t>
+          <t>People Who Lived Through The 1990s And 2000s Are Thoroughly Enjoying These 121 Posts (New Pics)</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0170-if-you-can-name-all-25-characters-from-these-silhouettes-you.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0170-people-who-lived-through-the-1990s-and-2000s-are-thoroughly-.jpg</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3017,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #032 (Jun 19, 2026)</t>
+          <t>64 Urban Hell Photos That Have People Wondering How These Places Came To Be</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0171-daily-word-search-game-032-jun-19-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0171-64-urban-hell-photos-that-have-people-wondering-how-these-pl.jpg</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3032,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Woman Shares A Pic Of The Dress She Wore To A Wedding And Asks If The Backlash Was Fair</t>
+          <t>45 Times People Asked Dumb Science Questions And The Internet Delivered Perfect Answers</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0172-woman-shares-a-pic-of-the-dress-she-wore-to-a-wedding-and-as.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0172-45-times-people-asked-dumb-science-questions-and-the-interne.jpg</t>
         </is>
       </c>
     </row>
@@ -3039,12 +3047,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>57 Heartwarming Posts From The Better Side Of The Internet</t>
+          <t>65 Men Recall The Exact Moment Everything Fell Apart</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0173-57-heartwarming-posts-from-the-better-side-of-the-internet.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0173-65-men-recall-the-exact-moment-everything-fell-apart.jpg</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3062,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>“Male Karen” Faces Karma After Harassing Dad For Helping Daughters In Women’s Restroom And Making Girl Cry</t>
+          <t>“We Don’t Believe Employees Should Own Pets”: 27 Bosses And Employers That Are Truly The Worst</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0174-male-karen-faces-karma-after-harassing-dad-for-helping-daugh.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0174-we-dont-believe-employees-should-own-pets-27-bosses-and-empl.jpg</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3077,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>“Could You Pass This General Science Quiz?”: Prove Your Brains Can Take It With 20 Questions</t>
+          <t>81 Funny Memes That People In Sales May Use To Explain What They Do To Their Families And Friends</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0175-could-you-pass-this-general-science-quiz-prove-your-brains-c.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0175-81-funny-memes-that-people-in-sales-may-use-to-explain-what-.jpg</t>
         </is>
       </c>
     </row>
@@ -3084,12 +3092,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>55 Terrifying Encounters People Wish They Could Rationally Explain</t>
+          <t>Man Says His Girlfriend Won’t Allow Him To Enter One Room In Her House, Is Shocked To Learn The Truth</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0176-55-terrifying-encounters-people-wish-they-could-rationally-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0176-man-says-his-girlfriend-wont-allow-him-to-enter-one-room-in-.jpg</t>
         </is>
       </c>
     </row>
@@ -3099,12 +3107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Brother’s Fiancée Throws A Full-Blown Tantrum Over A Dress That’s Not Even Hers</t>
+          <t>Bride Starts Having Doubts 9 Days Before The Wedding, Internet Pushes Her To Walk Away Now</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0177-brothers-fiancee-throws-a-full-blown-tantrum-over-a-dress-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0177-bride-starts-having-doubts-9-days-before-the-wedding-interne.jpg</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3122,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #093 (Jun 19, 2026)</t>
+          <t>Decide If These People Had A Valid Response In 10 Real-Life Situations</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0178-daily-guess-the-famous-person-game-093-jun-19-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0178-decide-if-these-people-had-a-valid-response-in-10-real-life-.jpg</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3137,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>This Artist Turns Family Banter, Bad Luck, And Daily Life Into Colorful Comics (24 New Comics)</t>
+          <t>Daily Guess The Country Game #028 (Jun 13, 2026)</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0179-this-artist-turns-family-banter-bad-luck-and-daily-life-into.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0179-daily-guess-the-country-game-028-jun-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3152,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>“Stands Like A Human”: 35 Surprising Facts And Stories About Animals That Might Teach You Something New</t>
+          <t>Daily Word Search Game #026 (Jun 13, 2026)</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0180-stands-like-a-human-35-surprising-facts-and-stories-about-an.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0180-daily-word-search-game-026-jun-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3167,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>55 Eerie Photos Of Abandoned Places And Forgotten Corners Of America By Brendon Burton</t>
+          <t>Daily Guess The Famous Person Game #087 (Jun 13, 2026)</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0181-55-eerie-photos-of-abandoned-places-and-forgotten-corners-of.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0181-daily-guess-the-famous-person-game-087-jun-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3182,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>“My Wedding Day”: 92 Times People Misread Social Cues So Badly, It Still Hurts To Remember</t>
+          <t>Man Reconnects With A Childhood Friend He Hasn’t Seen In 10 Years, Blows Up The Life He’s Built</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0182-my-wedding-day-92-times-people-misread-social-cues-so-badly-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0182-man-reconnects-with-a-childhood-friend-he-hasnt-seen-in-10-y.jpg</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3197,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>“What’s The Biggest Plot Twist In History?” (32 Posts)</t>
+          <t>Bride Bans Sister’s Boyfriend From Wedding For Disgusting And Ridiculous Reasons</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0183-whats-the-biggest-plot-twist-in-history-32-posts.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0183-bride-bans-sisters-boyfriend-from-wedding-for-disgusting-and.jpg</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3212,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>66 Poorly Designed Signs That Resulted In Hilarious Messages (New Pics)</t>
+          <t>Ben Stiller Faces Backlash After Viral Video Appears To Contradict His Message On Homelessness</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0184-66-poorly-designed-signs-that-resulted-in-hilarious-messages.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0184-ben-stiller-faces-backlash-after-viral-video-appears-to-cont.jpg</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3227,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Toxic Neighbor Learns $437K Lesson After Destroying Historic Orchard, Loses Her Home In The Process</t>
+          <t>40 Funny Pics Of Cats Being Themselves And Showing Off Their Shredded Masterpieces</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0185-toxic-neighbor-learns-437k-lesson-after-destroying-historic-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0185-40-funny-pics-of-cats-being-themselves-and-showing-off-their.jpg</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3242,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Teen Survives Being Kicked Out By Her Dad, Her Comeback Is So Remarkable He Is Now The One Begging</t>
+          <t>34 Scam Examples That Show America Is Living In A Completely Different Reality From Everyone Else</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0186-teen-survives-being-kicked-out-by-her-dad-her-comeback-is-so.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0186-34-scam-examples-that-show-america-is-living-in-a-completely.jpg</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3257,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Company Pins Missing $361 On The New Guy, Watches Thousands Go Up In Smoke When He Starts Talking</t>
+          <t>“Thank You Wave In Traffic”: 59 Social Contracts That Make Everyday Life Better</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0187-company-pins-missing-361-on-the-new-guy-watches-thousands-go.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0187-thank-you-wave-in-traffic-59-social-contracts-that-make-ever.jpg</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3272,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Teacher Refuses To Change Attendance Policy Even For 11YO’s Chemotherapy, Mom Takes Her Anger Online</t>
+          <t>Looksmaxxer Clavicular Just Had His 3rd Surgery, And People Are Getting Concerned About His Transformation</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0188-teacher-refuses-to-change-attendance-policy-even-for-11yos-c.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0188-looksmaxxer-clavicular-just-had-his-3rd-surgery-and-people-a.jpg</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3287,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Woman Says Husband’s Car Triggers Panic Attacks, Asks Couple To Text Before Leaving Home</t>
+          <t>“Do You Understand How The Body Works?”: Score 20/24 To Prove It In This Biology Quiz</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0189-woman-says-husbands-car-triggers-panic-attacks-asks-couple-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0189-do-you-understand-how-the-body-works-score-2024-to-prove-it-.jpg</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3302,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Surf Instructor Claps Back After Karen Demands She Cover Up Because Her Tween Feels Self-Conscious</t>
+          <t>59 Design Disasters That Are So Bad, They’re Honestly Kind Of Funny (New Pics)</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0190-surf-instructor-claps-back-after-karen-demands-she-cover-up-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0190-59-design-disasters-that-are-so-bad-theyre-honestly-kind-of-.jpg</t>
         </is>
       </c>
     </row>
@@ -3309,12 +3317,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Guy Lies About Allergy While On Tinder Date, Ends Up At The Emergency Room With $500 Bill</t>
+          <t>83 Examples Of “Awful Taste But Great Execution” That Left People Confused (New Pics)</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0191-guy-lies-about-allergy-while-on-tinder-date-ends-up-at-the-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0191-83-examples-of-awful-taste-but-great-execution-that-left-peo.jpg</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3332,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Guy Loses Trust In Wife After Living With The Consequences Of Her Impulsive Decisions For 10 Years</t>
+          <t>46 Times People Heard Such Genius Insults They Memorized Them</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0192-guy-loses-trust-in-wife-after-living-with-the-consequences-o.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0192-46-times-people-heard-such-genius-insults-they-memorized-the.jpg</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3347,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>“Lost A Bet With The Fashion Gods”: 20 Celebrity Outfits Compared With Their Original Runway Versions</t>
+          <t>63 Photos That Are So Great, They Deserve To Be Seen By More People</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0193-lost-a-bet-with-the-fashion-gods-20-celebrity-outfits-compar.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0193-63-photos-that-are-so-great-they-deserve-to-be-seen-by-more-.jpg</t>
         </is>
       </c>
     </row>
@@ -3354,12 +3362,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>A Guy Stole His Best Friend’s 8-Month Project Car Profit For A Bali Trip, Until A Text Trapped Him</t>
+          <t>Bride’s Wedding Guests Start Canceling One By One, The Reason Why Leaves Her Speechless</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0194-a-guy-stole-his-best-friends-8-month-project-car-profit-for-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0194-brides-wedding-guests-start-canceling-one-by-one-the-reason-.jpg</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3377,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>“They Don’t Eat Leftovers”: 56 Ignorant Middle-Class Phrases That They Need To Rethink</t>
+          <t>Woman Calls The Police After Learning What Her Sister Served For Lunch</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0195-they-dont-eat-leftovers-56-ignorant-middle-class-phrases-tha.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0195-woman-calls-the-police-after-learning-what-her-sister-served.jpg</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3392,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>“Are You A Geography Genius?”: Identify The Location Of These 19 Famous Places To Prove It</t>
+          <t>Toxic Fiancée Airs All Their Dirty Laundry, Guy’s Friends Finally Decide To Break Their Silence</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0196-are-you-a-geography-genius-identify-the-location-of-these-19.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0196-toxic-fiancee-airs-all-their-dirty-laundry-guys-friends-fina.jpg</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3407,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>67 Couches That Raise More Questions Than Any Piece Of Furniture Ever Should</t>
+          <t>From Hidden Objects To Impossible Perspectives: Challenge Your Vision With 15 Image Riddles</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0197-67-couches-that-raise-more-questions-than-any-piece-of-furni.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0197-from-hidden-objects-to-impossible-perspectives-challenge-you.jpg</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3422,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Margot Robbie Lost Her Cool When She Found Out Her Husband Was In Harry Potter Before They Met</t>
+          <t>Doctor Warns Of The Risks After “Looksmaxxer” Films Himself Using A Maxilla Expander</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0198-margot-robbie-lost-her-cool-when-she-found-out-her-husband-w.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0198-doctor-warns-of-the-risks-after-looksmaxxer-films-himself-us.jpg</t>
         </is>
       </c>
     </row>
@@ -3429,12 +3437,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>76 People Who Had The Audacity To Do What Everyone Else Was Thinking</t>
+          <t>29 Amazing Wall Transformations By Nuno Miles That Turn Urban Spaces Into Hyperrealistic Art</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0199-76-people-who-had-the-audacity-to-do-what-everyone-else-was-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0199-29-amazing-wall-transformations-by-nuno-miles-that-turn-urba.jpg</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3452,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>“I’m Personally 99% Against”: Uncle’s ‘Paranoid’ Advice To Niece Turns Out To Be A Life Saver</t>
+          <t>Daily Word Search Game #025 (Jun 12, 2026)</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/T/pins/0200-im-personally-99-against-uncles-paranoid-advice-to-niece-tur.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0200-daily-word-search-game-025-jun-12-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3546,114 +3554,115 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -467,12 +467,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55 Doctors Reveal The Health Problems Showing Up More Than Ever Before</t>
+          <t>MIL Hijacks The Wedding, Dresses Guests In White, And Leaves The Bride Out Of The Family Photos</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0001-55-doctors-reveal-the-health-problems-showing-up-more-than-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0001-mil-hijacks-the-wedding-dresses-guests-in-white-and-leaves-t.jpg</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>“This Hurts My Eyes”: 50 Attempts That Were Made But They Were Not Good Enough (New Pics)</t>
+          <t>Influencer Finally ID’d After Going Viral For Abhorrent Treatment Of Family Who Asked Him To Pick Up His Trash</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0002-this-hurts-my-eyes-50-attempts-that-were-made-but-they-were-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0002-influencer-finally-idd-after-going-viral-for-abhorrent-treat.jpg</t>
         </is>
       </c>
     </row>
@@ -497,12 +497,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bride Asks Mom Why She Wants The Wedding Delayed, Doesn’t Like The Answer</t>
+          <t>Hollywood Bias Exposed By Fans After Stephen King’s Horror Classic Reboot Triggers Outrage With First Look</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0003-bride-asks-mom-why-she-wants-the-wedding-delayed-doesnt-like.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0003-hollywood-bias-exposed-by-fans-after-stephen-kings-horror-cl.jpg</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Woman Refuses To Spend Vacation Babysitting Sister’s Kids, Family Drama Follows</t>
+          <t>Americans Obsessed With Trendy Snack Food Flying Off Shelves But Experts Warn Of Terrifying Side Effects</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0004-woman-refuses-to-spend-vacation-babysitting-sisters-kids-fam.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0004-americans-obsessed-with-trendy-snack-food-flying-off-shelves.jpg</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>If You Answer All 21 General Knowledge Questions, You’re Basically A Walking Encyclopedia</t>
+          <t>Study Reveals The Depressingly Dystopian Career Goals Of 60 Percent Of Kids</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0005-if-you-answer-all-21-general-knowledge-questions-youre-basic.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0005-study-reveals-the-depressingly-dystopian-career-goals-of-60-.jpg</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #087 (Jun 18, 2026)</t>
+          <t>“Looks Like A Big Child”: Here Are The Hilarious Reactions To Donald Trump’s “Special Helmet”</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0006-daily-guess-the-timeline-game-087-jun-18-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0006-looks-like-a-big-child-here-are-the-hilarious-reactions-to-d.jpg</t>
         </is>
       </c>
     </row>
@@ -557,12 +557,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Narcissistic Parents: A Survival Guide for Adult Children</t>
+          <t>Test Your Cinematic Memory &amp; Try To Recognize 16 Movies Just From Their First Scene</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0007-narcissistic-parents-a-survival-guide-for-adult-children.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0007-test-your-cinematic-memory-try-to-recognize-16-movies-just-f.jpg</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Only A Well-Read Person Can Answer All 20 Of These Questions On Classic Literature</t>
+          <t>Adult Star Bonnie Blue Describes How Participants Dealt With Her Baby Bump During 10-Hour July 4 Event</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0008-only-a-well-read-person-can-answer-all-20-of-these-questions.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0008-adult-star-bonnie-blue-describes-how-participants-dealt-with.jpg</t>
         </is>
       </c>
     </row>
@@ -587,12 +587,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shelter Dogs Are Finding New Homes After This Man Gives Them Backpack Rides Around NYC</t>
+          <t>Guy Who Has Visited Every Country On Earth Just Named The 5 Places Where He Felt Most Unsafe</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0009-shelter-dogs-are-finding-new-homes-after-this-man-gives-them.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0009-guy-who-has-visited-every-country-on-earth-just-named-the-5-.jpg</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #033 (Jun 18, 2026)</t>
+          <t>Bonnie Blue’s Former Coworker Spills The Tea On Her Life Before Fame</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0010-daily-guess-the-country-game-033-jun-18-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0010-bonnie-blues-former-coworker-spills-the-tea-on-her-life-befo.jpg</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31 Clever And Absurd Comics By John Atkinson That Put A Weird Spin On Random Everyday Thoughts</t>
+          <t>Test Your Art Knowledge By Guessing 16 Famous Artists Just By Their Self-Portraits</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0011-31-clever-and-absurd-comics-by-john-atkinson-that-put-a-weir.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0011-test-your-art-knowledge-by-guessing-16-famous-artists-just-b.jpg</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>This Cartoonist Created 39 Weird, Dark Humor Comics Full Of Bizarre Twists</t>
+          <t>78 Images That Refuse To Make Sense On The First, Second, Or Third Look</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0012-this-cartoonist-created-39-weird-dark-humor-comics-full-of-b.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0012-78-images-that-refuse-to-make-sense-on-the-first-second-or-t.jpg</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32 Wild And Unsettling Vintage Toy Designs By Shampoooty That Defy Norms</t>
+          <t>Daily Guess The Country Game #059 (Jul 14, 2026)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0013-32-wild-and-unsettling-vintage-toy-designs-by-shampoooty-tha.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0013-daily-guess-the-country-game-059-jul-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Best 100 Comics By Stephen Beals About Retail, Work Stress, And Customer Interactions (Part 1)</t>
+          <t>Experts Highlight A Strange New Benefit That Dark Chocolate Has, And Gymgoers Are Ecstatic</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0014-the-best-100-comics-by-stephen-beals-about-retail-work-stres.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0014-experts-highlight-a-strange-new-benefit-that-dark-chocolate-.jpg</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #031 (Jun 18, 2026)</t>
+          <t>Gay Couple’s Surrogacy Journey Turns Into Ugly Feud After They Sue Woman Who Carried Their Son</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0015-daily-word-search-game-031-jun-18-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0015-gay-couples-surrogacy-journey-turns-into-ugly-feud-after-the.jpg</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33 Wholesome Posts About Men Defining Masculinity In Their Own Way</t>
+          <t>24 Award-Winning Wildlife Photos Shared By The Artist Gallery</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0016-33-wholesome-posts-about-men-defining-masculinity-in-their-o.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0016-24-award-winning-wildlife-photos-shared-by-the-artist-galler.jpg</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27 Times A Perfectly Normal Person Turned Out To Have A Dark Side</t>
+          <t>17 New Funny Comics Depicting The Real-Life Challenges Of Lower-Class Society, By Mike Lewis</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0017-27-times-a-perfectly-normal-person-turned-out-to-have-a-dark.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0017-17-new-funny-comics-depicting-the-real-life-challenges-of-lo.jpg</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>69 “Comments You Can Hear” That Practically Read Themselves Out Loud</t>
+          <t>Elderly Couple Leaves Heartbreaking Message For Daughter Before Escaping Care Home</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0018-69-comments-you-can-hear-that-practically-read-themselves-ou.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0018-elderly-couple-leaves-heartbreaking-message-for-daughter-bef.jpg</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Doctor Exposes Shocking Studies On Women’s Health, And People Are Absolutely Furious</t>
+          <t>Daily Guess The Timeline Game #113 (Jul 14, 2026)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0019-doctor-exposes-shocking-studies-on-womens-health-and-people-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0019-daily-guess-the-timeline-game-113-jul-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>This Artist Captures The Chaos, Charm, And Confidence Of Pomeranians In 40 Comics</t>
+          <t>Groom Promises All 3 Sisters Bridesmaid Dresses, Bride Hands Out Rejection Letters Based On Weight</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0020-this-artist-captures-the-chaos-charm-and-confidence-of-pomer.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0020-groom-promises-all-3-sisters-bridesmaid-dresses-bride-hands-.jpg</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #092 (Jun 18, 2026)</t>
+          <t>Entitled Influencers Try To Use Luxe Hotel For Insta Pics, Badmouth The Venue When They’re Sent Home</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0021-daily-guess-the-famous-person-game-092-jun-18-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0021-entitled-influencers-try-to-use-luxe-hotel-for-insta-pics-ba.jpg</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>49 Last Minute Father’s Day Gifts That Are So Good Dad Will Never Know You Ordered Them Yesterday</t>
+          <t>Student Blames Everyone Around But Himself In His Failures, Demands A Solo Project And Fails Again</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0022-49-last-minute-fathers-day-gifts-that-are-so-good-dad-will-n.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0022-student-blames-everyone-around-but-himself-in-his-failures-d.jpg</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>40 Unsettling True Stories From “Oddly Horrifying” That Show How Dark The Real World Can Be (New Pics)</t>
+          <t>77 Quick, Clever, And Unexpected Comics From Joe Lennon (New Pics)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0023-40-unsettling-true-stories-from-oddly-horrifying-that-show-h.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0023-77-quick-clever-and-unexpected-comics-from-joe-lennon-new-pi.jpg</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30 Wild Stories Of People Whose Double Lives Eventually Caught Up With Them</t>
+          <t>Boyfriend Secretly Blocks Woman’s Male Friends On Facebook, Claims It’s Just Being “Protective”</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0024-30-wild-stories-of-people-whose-double-lives-eventually-caug.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0024-boyfriend-secretly-blocks-womans-male-friends-on-facebook-cl.jpg</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>“May God Punish You For How You Treated Me”: 76 Online Reviews That Are Funnier Than They Should Be</t>
+          <t>Struggling Dad Blames Wife For Sixth Pregnancy, Brother Gives Him A Brutal Reality Check</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0025-may-god-punish-you-for-how-you-treated-me-76-online-reviews-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0025-struggling-dad-blames-wife-for-sixth-pregnancy-brother-gives.jpg</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>“What Is The Dumbest Thing You Have Been Told Is Not Manly Or Not Feminine?” (62 Answers)</t>
+          <t>IT Worker Takes Down Buffoon Accountant With Clever Plan, Says “Network’s Down” Right Back At Her</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0026-what-is-the-dumbest-thing-you-have-been-told-is-not-manly-or.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0026-it-worker-takes-down-buffoon-accountant-with-clever-plan-say.jpg</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guy Dangles Engagement Ring To Get GF To Share Authorship Of Her Book, Won’t Take No For An Answer</t>
+          <t>Millie Bobby Brown’s Lie Detector Test Takes Controversial Turn After She’s Asked About Eating Her Animals</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0027-guy-dangles-engagement-ring-to-get-gf-to-share-authorship-of.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0027-millie-bobby-browns-lie-detector-test-takes-controversial-tu.jpg</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Man Walks In On Gym Bros Hooking Up In The Steam Room, Gets Blamed For Ruining Their Alpha Image</t>
+          <t>From Sand To Packaging, Here Are 34 Unpopular Industries That Actually Make Millions</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0028-man-walks-in-on-gym-bros-hooking-up-in-the-steam-room-gets-b.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0028-from-sand-to-packaging-here-are-34-unpopular-industries-that.jpg</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Controlling Parents Hijack Son’s Beach Trip, Call Him Ungrateful When He Cancels The Whole Thing</t>
+          <t>Woman Serves Mean Teammates The Best Brownies Ever, Keeps Her Recipe Secret As Petty Payback</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0029-controlling-parents-hijack-sons-beach-trip-call-him-ungratef.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0029-woman-serves-mean-teammates-the-best-brownies-ever-keeps-her.jpg</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guy Cheats On Wife With A Coworker, Her Kids Methodically Destroy Everything He Built</t>
+          <t>Celebrity Birthdays Today, July 14, 2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0030-guy-cheats-on-wife-with-a-coworker-her-kids-methodically-des.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0030-celebrity-birthdays-today-july-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mom Gets Spoiled All Day On Mother’s Day, Still Finds A Reason To Throw A Massive Tantrum</t>
+          <t>NYT Pips Hints, Answers For 14-July-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0031-mom-gets-spoiled-all-day-on-mothers-day-still-finds-a-reason.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0031-nyt-pips-hints-answers-for-14-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17YO Traumatized With Dad’s Reaction To Her Illness, Ends Up Keeping It A Secret But Drama Ensues</t>
+          <t>Spelling Bee Hints, Answers For 14-July-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0032-17yo-traumatized-with-dads-reaction-to-her-illness-ends-up-k.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0032-spelling-bee-hints-answers-for-14-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>35 Times A Friend Did One Thing So Disturbing It Changed How People Saw Them Forever</t>
+          <t>NYT Mini Crossword Hints And Answers For 14-July-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0033-35-times-a-friend-did-one-thing-so-disturbing-it-changed-how.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0033-nyt-mini-crossword-hints-and-answers-for-14-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Guy Controls Stepdaughter With Ridiculous Rules, Cries Foul As She Finally Cuts Ties For Good</t>
+          <t>NYT Strands Hints And Answers For 14-July-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0034-guy-controls-stepdaughter-with-ridiculous-rules-cries-foul-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0034-nyt-strands-hints-and-answers-for-14-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Employee Asks For A Raise For Years, Boss Learns How Expensive “No” Can Be</t>
+          <t>NYT Connections Hints And Answers For 14-July-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0035-employee-asks-for-a-raise-for-years-boss-learns-how-expensiv.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0035-nyt-connections-hints-and-answers-for-14-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #086 (Jun 17, 2026)</t>
+          <t>Wordle #1851: Hints &amp; Answer (Jul 14, 2026)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0036-daily-guess-the-timeline-game-086-jun-17-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0036-wordle-1851-hints-answer-jul-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>“Is Your Disney IQ Above Average?”: Prove It By Guessing 16 Characters From Their Eyes</t>
+          <t>Wordle #1851: Hints &amp; Answer (Jul 14, 2026)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-is-your-disney-iq-above-average-prove-it-by-guessing-16-char.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1851-hints-answer-jul-14-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Guy Meets The Wife Of His Ex-Wife’s Affair Partner And Realizes Something</t>
+          <t>Claudia J. Kennedy: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0038-guy-meets-the-wife-of-his-ex-wifes-affair-partner-and-realiz.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0038-claudia-j-kennedy-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>“I Don’t Have A Red Flag”: 27 Questions That Will Probably Prove You Wrong</t>
+          <t>Maulana Karenga: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0039-i-dont-have-a-red-flag-27-questions-that-will-probably-prove.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0039-maulana-karenga-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Millionaire Connected To UK Royals Arrested 9 Years After Jogger Caught On Video pushing Woman In Front Of Bus</t>
+          <t>Nancy Olson: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0040-millionaire-connected-to-uk-royals-arrested-9-years-after-jo.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0040-nancy-olson-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>These 109 Bakers Took Dessert Decorating To An Entirely Different Level (New Pics)</t>
+          <t>Kyle Gass: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0041-these-109-bakers-took-dessert-decorating-to-an-entirely-diff.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0041-kyle-gass-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A Lifelong Bond Between Siblings Crumbles When Woman Realizes Brother Kept A Major Secret Only From Her</t>
+          <t>Jackie Earle Haley: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0042-a-lifelong-bond-between-siblings-crumbles-when-woman-realize.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0042-jackie-earle-haley-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Update In Case Of Imprisoned Woman Who Set Her Male Friend On Fire Over ‘Misogynist’ Comment</t>
+          <t>Howard Lutnick: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0043-update-in-case-of-imprisoned-woman-who-set-her-male-friend-o.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0043-howard-lutnick-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>“Overstimulating Americanness”: 79 Parts Of US Culture Tourists Weren’t Ready For</t>
+          <t>Matthew Fox: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0044-overstimulating-americanness-79-parts-of-us-culture-tourists.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0044-matthew-fox-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>75 Times Urban Planners Failed To Predict What People Want, And It Resulted In ‘Desire Paths’ Around The City (New Pics)</t>
+          <t>Jane Lynch: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0045-75-times-urban-planners-failed-to-predict-what-people-want-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0045-jane-lynch-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #032 (Jun 17, 2026)</t>
+          <t>Phoebe Waller-Bridge: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0046-daily-guess-the-country-game-032-jun-17-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0046-phoebe-waller-bridge-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>From Public Meltdowns To Strange Confessions, 38 People Share How Their Relationships Ended</t>
+          <t>Dan Reynolds: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0047-from-public-meltdowns-to-strange-confessions-38-people-share.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0047-dan-reynolds-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>“I Want People To Feel More Understood”: 30 New Relatable Comics By Krysten Bevilaqua</t>
+          <t>Influencer Exposes The Five “Biggest Mistakes” American Tourists Make With Their Outfits In Europe</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0048-i-want-people-to-feel-more-understood-30-new-relatable-comic.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0048-influencer-exposes-the-five-biggest-mistakes-american-touris.jpg</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>“Can You Solve Them All?”: 15 Math Puzzles That Are Trickier Than They First Seem</t>
+          <t>Why Gen Z Isn’t Watching Superhero Movies Explained After Furious Fans Blast New ‘Avengers’ Poster</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0049-can-you-solve-them-all-15-math-puzzles-that-are-trickier-tha.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0049-why-gen-z-isnt-watching-superhero-movies-explained-after-fur.jpg</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>31 New Comedic Animal Portraits By Alison Friend That Make Pets Look Like Tiny Eccentric Nobles</t>
+          <t>Tom Cruise’s Incredible Transformation Hailed As Oscar-Worthy After Trailer For Next Movie Drops</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0050-31-new-comedic-animal-portraits-by-alison-friend-that-make-p.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0050-tom-cruises-incredible-transformation-hailed-as-oscar-worthy.jpg</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>64 Random Silly Memes That Might Bring A Smile To Anyone Feeling Overwhelmed Today</t>
+          <t>David Beckham Forced To Defend Wife Victoria After Her Behavior At World Cup Match Sparked Wave Of Mockery</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0051-64-random-silly-memes-that-might-bring-a-smile-to-anyone-fee.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0051-david-beckham-forced-to-defend-wife-victoria-after-her-behav.jpg</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #030 (Jun 17, 2026)</t>
+          <t>This Photographer Captured The Beauty Of Europe’s Disappearing Countryside Traditions (19 Pics)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0052-daily-word-search-game-030-jun-17-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0052-this-photographer-captured-the-beauty-of-europes-disappearin.jpg</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30 Unfiltered Images That Show Real Life Across The Globe By This Street Photographer (New Pics)</t>
+          <t>New Bombshell ‘Evidence’ Could Allegedly Clear Scott Peterson In The Infamous Homicide Of His Wife Laci</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0053-30-unfiltered-images-that-show-real-life-across-the-globe-by.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0053-new-bombshell-evidence-could-allegedly-clear-scott-peterson-.jpg</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rather Than Decorating The Body, I Design Tattoos That Work With It (53 Pics)</t>
+          <t>Celebrity Birthdays Today, July 13, 2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0054-rather-than-decorating-the-body-i-design-tattoos-that-work-w.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0054-celebrity-birthdays-today-july-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>103 Tattoo Fails That Are Impossible To Ignore (New Pics)</t>
+          <t>NYT Pips Hints, Answers For 13-July-2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0055-103-tattoo-fails-that-are-impossible-to-ignore-new-pics.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0055-nyt-pips-hints-answers-for-13-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>“It Was A Cult”: 49 Times People Realized That Something Was Very Wrong And They Needed To Leave</t>
+          <t>NYT Mini Crossword Hints And Answers For 13-July-2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0056-it-was-a-cult-49-times-people-realized-that-something-was-ve.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0056-nyt-mini-crossword-hints-and-answers-for-13-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bride Couldn’t Believe What MIL Did At The Wedding, Neither Could The Guests</t>
+          <t>NYT Strands Hints And Answers For 13-July-2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0057-bride-couldnt-believe-what-mil-did-at-the-wedding-neither-co.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0057-nyt-strands-hints-and-answers-for-13-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>82 Incredible Historical Finds That Left People Staring In Disbelief (New Pics)</t>
+          <t>Wordle #1850: Hints &amp; Answer (Jul 13, 2026)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0058-82-incredible-historical-finds-that-left-people-staring-in-d.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0058-wordle-1850-hints-answer-jul-13-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #091 (Jun 17, 2026)</t>
+          <t>NYT Connections Hints And Answers For 13-July-2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0059-daily-guess-the-famous-person-game-091-jun-17-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0059-nyt-connections-hints-and-answers-for-13-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>56 Women Share The Comments They Received About Their Bodies That They Didn’t See Coming</t>
+          <t>Spelling Bee Hints, Answers For 13-July-2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0060-56-women-share-the-comments-they-received-about-their-bodies.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0060-spelling-bee-hints-answers-for-13-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Conservative Law Allows Pharmacists To Deny Service, But One 85-Year-Old’s Epic Response Leaves Them Stunned</t>
+          <t>Colton Haynes: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0061-conservative-law-allows-pharmacists-to-deny-service-but-one-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0061-colton-haynes-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Exhausted Wife Works Two Jobs While Unemployed Husband Lives In Digital Reality Thinking He’s Productive</t>
+          <t>José Andrés: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0062-exhausted-wife-works-two-jobs-while-unemployed-husband-lives.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0062-jose-andres-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>42 Experiences With The Youngest Generation That Make People Feel The World Is Doomed</t>
+          <t>Deborah Cox: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0063-42-experiences-with-the-youngest-generation-that-make-people.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0063-deborah-cox-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dad Spent All His Money On Stepdaughter While Watching Bio Kids Suffer, Son Devastated By The Truth</t>
+          <t>Leon Bridges: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0064-dad-spent-all-his-money-on-stepdaughter-while-watching-bio-k.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0064-leon-bridges-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Toxic Boss Forced To Close Business After Insulting Top Performer, Ends Up Having His Clients Stolen</t>
+          <t>Cameron Crowe: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0065-toxic-boss-forced-to-close-business-after-insulting-top-perf.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0065-cameron-crowe-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Delulu Mom Wants A Perfect Blended Family, Throws A Hissy Fit When Kids Reject Her Ideology</t>
+          <t>Tom Kenny: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0066-delulu-mom-wants-a-perfect-blended-family-throws-a-hissy-fit.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0066-tom-kenny-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Postpartum Wife’s 1000 Tinder Matches Shock Hubby, But The Truth Shatters Him More</t>
+          <t>Cheech Marin: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0067-postpartum-wifes-1000-tinder-matches-shock-hubby-but-the-tru.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0067-cheech-marin-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Woman Can’t Figure Out Why Her Wedding News Falls Flat, Best Friend Knows The Uncomfortable Truth</t>
+          <t>Ken Jeong: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0068-woman-cant-figure-out-why-her-wedding-news-falls-flat-best-f.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0068-ken-jeong-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Family Bows To Demanding MIL’s Every Wish, Woman Becomes The First To Stand Up To Her</t>
+          <t>Patrick Stewart: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0069-family-bows-to-demanding-mils-every-wish-woman-becomes-the-f.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0069-patrick-stewart-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Unhinged Woman Sparks Drama With Her Racism All Because Her Crush Drew Her Bestie’s Portrait</t>
+          <t>Harrison Ford: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0070-unhinged-woman-sparks-drama-with-her-racism-all-because-her-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0070-harrison-ford-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cranky Neighbor Sparks Property Feud, Creates Huge Mess For Himself Instead</t>
+          <t>Judge Denies 18-Year-Old Attacker’s Last Request Before Life Prison Sentence For Ending 15YO Girl’s Life</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0071-cranky-neighbor-sparks-property-feud-creates-huge-mess-for-h.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0071-judge-denies-18-year-old-attackers-last-request-before-life-.jpg</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>“Your Body Will Simply Give Up”: 38 Human Body Facts That Might Make You Scared To Be Alive</t>
+          <t>Amy Schumer Breaks Silence On Her Most-Talked-About Intimate Scene With John Cena</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0072-your-body-will-simply-give-up-38-human-body-facts-that-might.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0072-amy-schumer-breaks-silence-on-her-most-talked-about-intimate.jpg</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #085 (Jun 16, 2026)</t>
+          <t>Celebrity Birthdays Today, July 12, 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0073-daily-guess-the-timeline-game-085-jun-16-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0073-celebrity-birthdays-today-july-12-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mom Thinks Everyone Else Is Overreacting To Daughter’s Behavior, Commenters Disagree</t>
+          <t>Spelling Bee Hints, Answers For 12-July-2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0074-mom-thinks-everyone-else-is-overreacting-to-daughters-behavi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0074-spelling-bee-hints-answers-for-12-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>“She Refused To Speak To The Staff”: 35 Celebrity Encounters That Were A Lot To Witness</t>
+          <t>Wordle #1849: Hints &amp; Answer (Jul 12, 2026)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0075-she-refused-to-speak-to-the-staff-35-celebrity-encounters-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0075-wordle-1849-hints-answer-jul-12-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Woman Survives A Workplace Emergency, Then Finds Herself In Even More Trouble</t>
+          <t>NYT Pips Hints, Answers For 12-July-2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0076-woman-survives-a-workplace-emergency-then-finds-herself-in-e.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0076-nyt-pips-hints-answers-for-12-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>19 Celebrities Showed Up To Watch UFC At The White House, And The Guest List Is A Lot To Process</t>
+          <t>NYT Connections Hints And Answers For 12-July-2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0077-19-celebrities-showed-up-to-watch-ufc-at-the-white-house-and.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0077-nyt-connections-hints-and-answers-for-12-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Passenger Tormented By Racist Woman On Flight Gets An Upgrade, She Gets Shut Down By The Crew</t>
+          <t>NYT Mini Crossword Hints And Answers For 12-July-2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0078-passenger-tormented-by-racist-woman-on-flight-gets-an-upgrad.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0078-nyt-mini-crossword-hints-and-answers-for-12-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21 Mind-Bending Dilemmas That’ll Challenge Your Morals: Vote Now &amp; See Where You Stand</t>
+          <t>NYT Strands Hints And Answers For 12-July-2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0079-21-mind-bending-dilemmas-thatll-challenge-your-morals-vote-n.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0079-nyt-strands-hints-and-answers-for-12-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>53 Toxic Friends Who Hurt People In Ways They Never Saw Coming</t>
+          <t>Steve Howey: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0080-53-toxic-friends-who-hurt-people-in-ways-they-never-saw-comi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0080-steve-howey-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Children Of Karen Parents Are Sharing Their Wildest Stories, And They’re Brutal</t>
+          <t>Natalie Martinez: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0081-children-of-karen-parents-are-sharing-their-wildest-stories-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0081-natalie-martinez-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trauma Bonding: Signs, Stages, and How to Break Free</t>
+          <t>Phil Lord: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0082-trauma-bonding-signs-stages-and-how-to-break-free.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0082-phil-lord-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Narcissistic Guy Refuses To Pay Spousal Support And Takes Ex To Court, Ends Up Paying With 401k</t>
+          <t>Cheryl Ladd: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0083-narcissistic-guy-refuses-to-pay-spousal-support-and-takes-ex.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0083-cheryl-ladd-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I Illustrate The Hilarious Reality Of A Rescue Dog And A Cat Living Together (25 New Comics)</t>
+          <t>Lee Byung-hun: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0084-i-illustrate-the-hilarious-reality-of-a-rescue-dog-and-a-cat.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0084-lee-byung-hun-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #031 (Jun 16, 2026)</t>
+          <t>Malala Yousafzai: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0085-daily-guess-the-country-game-031-jun-16-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0085-malala-yousafzai-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>This Photographer Captured 42 Dreamlike Images Of Antarctica</t>
+          <t>Loni Love: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0086-this-photographer-captured-42-dreamlike-images-of-antarctica.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0086-loni-love-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>39 Captivating Travel Photos From The 2025 Chromatic Awards That Show How Diverse The World Is</t>
+          <t>Rachel Brosnahan: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0087-39-captivating-travel-photos-from-the-2025-chromatic-awards-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0087-rachel-brosnahan-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>“Can You Still Solve Basic Equations?”: Ace This 20-Question Math Quiz And Reveal The Truth</t>
+          <t>Topher Grace: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0088-can-you-still-solve-basic-equations-ace-this-20-question-mat.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0088-topher-grace-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>This Page Shared 26 Heartwarming Animal Moments From Around The World (New Pics)</t>
+          <t>Michelle Rodriguez: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0089-this-page-shared-26-heartwarming-animal-moments-from-around-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0089-michelle-rodriguez-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>25 Remarkable Dog Rescue Transformations Shared By NIRA That Show The Power Of A Second Chance</t>
+          <t>Celebrity Birthdays Today, July 11, 2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0090-25-remarkable-dog-rescue-transformations-shared-by-nira-that.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0090-celebrity-birthdays-today-july-11-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #029 (Jun 16, 2026)</t>
+          <t>NYT Pips Hints, Answers For 11-July-2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0091-daily-word-search-game-029-jun-16-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0091-nyt-pips-hints-answers-for-11-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>23 Hilarious Father’s Day Gifts For The Dad Whose Sense Of Humor Is The Best Thing He Passed Down</t>
+          <t>NYT Mini Crossword Hints And Answers For 11-July-2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0092-23-hilarious-fathers-day-gifts-for-the-dad-whose-sense-of-hu.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0092-nyt-mini-crossword-hints-and-answers-for-11-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30 New Comics By Brian Gordon Showcasing The Funny Side Of Parenting</t>
+          <t>Spelling Bee Hints, Answers For 11-July-2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0093-30-new-comics-by-brian-gordon-showcasing-the-funny-side-of-p.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0093-spelling-bee-hints-answers-for-11-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Emily Ratajkowski Faces Backlash Over Essay About Single Motherhood Accompanied By Bizarre Breastfeeding Photo</t>
+          <t>Wordle #1848: Hints &amp; Answer (Jul 11, 2026)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0094-emily-ratajkowski-faces-backlash-over-essay-about-single-mot.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0094-wordle-1848-hints-answer-jul-11-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>67 Brutally Honest Posts From Millennials On Social Media (New Pics)</t>
+          <t>NYT Strands Hints And Answers For 11-July-2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0095-67-brutally-honest-posts-from-millennials-on-social-media-ne.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0095-nyt-strands-hints-and-answers-for-11-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>63 Awkward Texts That Are So Bad It’s Funny (New Pics)</t>
+          <t>NYT Connections Hints And Answers For 11-July-2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0096-63-awkward-texts-that-are-so-bad-its-funny-new-pics.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0096-nyt-connections-hints-and-answers-for-11-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>“Unsure About Dinosaurs”: 50 People Who Dated Morons Reveal Their Dumbest Beliefs</t>
+          <t>Andrew Bird: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0097-unsure-about-dinosaurs-50-people-who-dated-morons-reveal-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0097-andrew-bird-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>This Instagram Account Shares Hilarious Design Fails, Here Are 91 Of The Best (New Pics)</t>
+          <t>Mindy Sterling: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0098-this-instagram-account-shares-hilarious-design-fails-here-ar.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0098-mindy-sterling-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Spiteful Grandma Spills Decades-Old Secret In Most Brutal Way Possible And Faces Immediate Family Exile</t>
+          <t>Suzanne Vega: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0099-spiteful-grandma-spills-decades-old-secret-in-most-brutal-wa.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0099-suzanne-vega-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>This Page Shared 65 Irresistible Pics Of Baby Animals And Their Moms</t>
+          <t>Michael Rosenbaum: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0100-this-page-shared-65-irresistible-pics-of-baby-animals-and-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0100-michael-rosenbaum-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #090 (Jun 16, 2026)</t>
+          <t>Stephen Lang: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0101-daily-guess-the-famous-person-game-090-jun-16-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0101-stephen-lang-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>We Prepared 26 Pop Culture Questions From A To Z – Anything Above 22 Is An Excellent Score</t>
+          <t>Justin Chambers: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0102-we-prepared-26-pop-culture-questions-from-a-to-z-anything-ab.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0102-justin-chambers-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30 Times Folks Online Were Disturbed By The People Their Friends Were Dating</t>
+          <t>Alessia Cara: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0103-30-times-folks-online-were-disturbed-by-the-people-their-fri.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0103-alessia-cara-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>71 Times People Thought They Took Normal Photos Until They Turned Into Hilarious ‘When You See It’ Moments (New Pics)</t>
+          <t>Richie Sambora: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0104-71-times-people-thought-they-took-normal-photos-until-they-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0104-richie-sambora-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19YO Gets Dismissed By Know-It-All Nurse, Returns A Week Later With A Huge Infection Instead</t>
+          <t>Lisa Rinna: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0105-19yo-gets-dismissed-by-know-it-all-nurse-returns-a-week-late.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0105-lisa-rinna-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Aunt Tired Of Playing Emergency Contact For 5YO In Constant Trouble, Demands Parents Face Reality</t>
+          <t>Lil’ Kim: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0106-aunt-tired-of-playing-emergency-contact-for-5yo-in-constant-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0106-lil-kim-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VIP Passenger Picks Drinking Over Taking Care Of Her Kids, Pilot Ends Up Teaching Her A Lesson</t>
+          <t>Behind History’s Craze When Being Bigger Was The Height Of Fashion And Women Stuffed Dresses To Appear Larger</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0107-vip-passenger-picks-drinking-over-taking-care-of-her-kids-pi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0107-behind-historys-craze-when-being-bigger-was-the-height-of-fa.jpg</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Couple Are Warned About Nightmare Neighbor, Move In Across The Road Anyway, Regret It Immediately</t>
+          <t>Christopher Nolan’s “Tone-Deaf” Defense Of ‘The Odyssey’ Backlash Infuriates Fans: “Pure Hollywood Arrogance”</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0108-couple-are-warned-about-nightmare-neighbor-move-in-across-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0108-christopher-nolans-tone-deaf-defense-of-the-odyssey-backlash.jpg</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vicious Aunt Berates “Unladylike” Niece, Doesn’t Realize She’s Saying Goodbye To Her Own Cash Flow</t>
+          <t>Adult Worker Exposes Disturbing Consequences For The Clients Of Her Most Extreme Service</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0109-vicious-aunt-berates-unladylike-niece-doesnt-realize-shes-sa.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0109-adult-worker-exposes-disturbing-consequences-for-the-clients.jpg</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mom Lets Stepkids Make Daughter Miserable For Years, Suddenly Wants A Second Chance When She’s Gone</t>
+          <t>Children’s Book Removed From School After Mom Notices Bizarre Detail She Says No Kid Should Read</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0110-mom-lets-stepkids-make-daughter-miserable-for-years-suddenly.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0110-childrens-book-removed-from-school-after-mom-notices-bizarre.jpg</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>49 People With Jobs So Strange Most People Don’t Know They Exist</t>
+          <t>Star In Her 60s Reveals Relationship With 22-Year-Old, And People Aren’t Taking It All</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0111-49-people-with-jobs-so-strange-most-people-dont-know-they-ex.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0111-star-in-her-60s-reveals-relationship-with-22-year-old-and-pe.jpg</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>73 Cursed Images From This Weird Corner Of The Internet (New Pics)</t>
+          <t>Striking Comparison Between Charlize Theron And Anne Hathaway Provokes Discussion On Beauty Standards</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0112-73-cursed-images-from-this-weird-corner-of-the-internet-new-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0112-striking-comparison-between-charlize-theron-and-anne-hathawa.jpg</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Barron Trump’s UFC Appearance Fuels Concern And Wild Speculation About His Changed Look: “Absolutely Miserable”</t>
+          <t>Ever Thinner Celebrities Trend In Hollywood Grows As Charlize Theron Is The Latest To Trigger Worry From Fans</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0113-barron-trumps-ufc-appearance-fuels-concern-and-wild-speculat.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0113-ever-thinner-celebrities-trend-in-hollywood-grows-as-charliz.jpg</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>50 Funny Cat Memes That Prove Life Is Better When Cats Are Being Weird</t>
+          <t>Family Of Mackenzie Shirilla’s Victim Breaks Silence After Her Latest Prison Selfie Stirs Controversy</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0114-50-funny-cat-memes-that-prove-life-is-better-when-cats-are-b.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0114-family-of-mackenzie-shirillas-victim-breaks-silence-after-he.jpg</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>“Never Expected Me To Turn Her Own Logic Against Her”: Woman Shocks MIL With A Savage Comeback</t>
+          <t>Celebrity Birthdays Today, July 10, 2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0115-never-expected-me-to-turn-her-own-logic-against-her-woman-sh.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0115-celebrity-birthdays-today-july-10-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>“If Your Arm Is Gone, It’s A Jaguar”: 73 Animal Facts That Sent Us Down A Rabbit Hole For Hours</t>
+          <t>NYT Pips Hints, Answers For 10-July-2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0116-if-your-arm-is-gone-its-a-jaguar-73-animal-facts-that-sent-u.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0116-nyt-pips-hints-answers-for-10-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>‘Karen’ Proves That Some Parents Need To Snap Back To Reality After She Attacks Disabled Person</t>
+          <t>Wordle #1847: Hints &amp; Answer (Jul 10, 2026)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0117-karen-proves-that-some-parents-need-to-snap-back-to-reality-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0117-wordle-1847-hints-answer-jul-10-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #084 (Jun 15, 2026)</t>
+          <t>NYT Mini Crossword Hints And Answers For 10-July-2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0118-daily-guess-the-timeline-game-084-jun-15-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0118-nyt-mini-crossword-hints-and-answers-for-10-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Woman Shocked That She Might Be “Stealing Friend’s Boyfriend,” The Truth Is More Bizarre Than She Expected</t>
+          <t>NYT Connections Hints And Answers For 10-July-2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0119-woman-shocked-that-she-might-be-stealing-friends-boyfriend-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0119-nyt-connections-hints-and-answers-for-10-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>33 Folks Who Believed Their Friends Were Just “Nice Peeps,” Until Some Discovery Proved The Opposite</t>
+          <t>NYT Strands Hints And Answers For 10-July-2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0120-33-folks-who-believed-their-friends-were-just-nice-peeps-unt.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0120-nyt-strands-hints-and-answers-for-10-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>“Never Came Back To School”: 51 Times The Class Clown Took It Too Far And Faced The Consequences</t>
+          <t>Spelling Bee Hints, Answers For 10-July-2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0121-never-came-back-to-school-51-times-the-class-clown-took-it-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0121-spelling-bee-hints-answers-for-10-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Only True Music Fans Can Name All 25 Iconic Titles From A Blurry Image</t>
+          <t>Vivek Murthy: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0122-only-true-music-fans-can-name-all-25-iconic-titles-from-a-bl.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0122-vivek-murthy-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>We Highly Doubt You Can Beat The Average U.S. Student – Prove Us Wrong In 18 Questions</t>
+          <t>James Rolfe: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0123-we-highly-doubt-you-can-beat-the-average-us-student-prove-us.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0123-james-rolfe-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Woman Finds Out She’s No Longer Invited To Friend’s Wedding, Karma Hits Right Before The Big Day</t>
+          <t>Arlo Guthrie: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0124-woman-finds-out-shes-no-longer-invited-to-friends-wedding-ka.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0124-arlo-guthrie-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>57 Hilariously Random Screenshots That Were Too Funny Not To Share (New Pics)</t>
+          <t>Mavis Staples: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0125-57-hilariously-random-screenshots-that-were-too-funny-not-to.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0125-mavis-staples-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>“Is It Tokyo Or Seoul?”: Challenge Your Memory Of The Capitals With 18 Borderless Maps</t>
+          <t>Gong Yoo: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0126-is-it-tokyo-or-seoul-challenge-your-memory-of-the-capitals-w.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0126-gong-yoo-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #030 (Jun 15, 2026)</t>
+          <t>Isabela Merced: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0127-daily-guess-the-country-game-030-jun-15-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0127-isabela-merced-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>If You Like Dry Humor, Here Are 58 New One-Panel Comics By Graham Annable To Enjoy</t>
+          <t>Adrian Grenier: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0128-if-you-like-dry-humor-here-are-58-new-one-panel-comics-by-gr.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0128-adrian-grenier-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>43 Underwater Oil Paintings By This Artist, So Beautiful They Feel Like Memories In Motion</t>
+          <t>Chiwetel Ejiofor: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0129-43-underwater-oil-paintings-by-this-artist-so-beautiful-they.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0129-chiwetel-ejiofor-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #028 (Jun 15, 2026)</t>
+          <t>Sofía Vergara: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0130-daily-word-search-game-028-jun-15-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0130-sofia-vergara-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>‘House Of The Dragon’ Season 3 Cast Guide: Every New and Returning Character</t>
+          <t>Jessica Simpson: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0131-house-of-the-dragon-season-3-cast-guide-every-new-and-return.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0131-jessica-simpson-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>55 Memes Shared By The ‘Ancient Cringe’ Page That Turn Historical Art Into Relatable Comedy</t>
+          <t>Experts Reveal Lifestyle Factors Fueling Multiple Sclerosis As Christina Applegate And Selma Blair Struggle</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0132-55-memes-shared-by-the-ancient-cringe-page-that-turn-histori.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0132-experts-reveal-lifestyle-factors-fueling-multiple-sclerosis-.jpg</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>30 Futuristic Chrome Tattoos By This Artist That Look Like They Were Imported From The Future</t>
+          <t>Tourist’s Dream Vacation Takes Nightmare Turn After She’s Kidnapped Twice In One Day: “I Just Ran And Ran”</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0133-30-futuristic-chrome-tattoos-by-this-artist-that-look-like-t.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0133-tourists-dream-vacation-takes-nightmare-turn-after-shes-kidn.jpg</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #089 (Jun 15, 2026)</t>
+          <t>Adult Star Lily Phillips Turns Heads With Marriage Vow As Boyfriend Breaks Silence On Her Job: “I’m Proud”</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0134-daily-guess-the-famous-person-game-089-jun-15-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0134-adult-star-lily-phillips-turns-heads-with-marriage-vow-as-bo.jpg</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>“What Is Something That Is Highly Likely To Happen In The Next 10 Years That Everyone Is Completely Ignoring?” (67 Answers)</t>
+          <t>After Sleeping With Bonnie Blue At Her Baby Shower, Man Sparks Outrage With Girlfriend Twist That Stuns Netizens</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0135-what-is-something-that-is-highly-likely-to-happen-in-the-nex.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0135-after-sleeping-with-bonnie-blue-at-her-baby-shower-man-spark.jpg</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>We All Make Mistakes, But These 60 Huge Fails Hurt To Laugh At (New Pics)</t>
+          <t>Christopher Nolan’s ‘The Odyssey’ Is Somehow Even Worse Than Anyone Imagined As Fans Lose It Over New Photo</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0136-we-all-make-mistakes-but-these-60-huge-fails-hurt-to-laugh-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0136-christopher-nolans-the-odyssey-is-somehow-even-worse-than-an.jpg</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Regretful Husband Deserts His Marriage For A Younger Fantasy, And Now He Can’t Handle The Reality</t>
+          <t>Italian PM Giorgia Meloni Stuns With Bold Reaction After Trump’s NATO “Family Photo” Snub</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0137-regretful-husband-deserts-his-marriage-for-a-younger-fantasy.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0137-italian-pm-giorgia-meloni-stuns-with-bold-reaction-after-tru.jpg</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>New Mom Shocked After Half-Sis Who Struggles With Infertility Said Newborn Was Hers</t>
+          <t>Urologist Explains What ‘Normal’ Private Parts Actually Look Like As He Urges People To Be Aware Of ‘Red Flag’</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0138-new-mom-shocked-after-half-sis-who-struggles-with-infertilit.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0138-urologist-explains-what-normal-private-parts-actually-look-l.jpg</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>20 Harsh Reality Checks From The “Awful Everything” Group That Might Change Your View On Things (New Pics)</t>
+          <t>Doctor Sends Alert After ‘Holding Out For A Hero’ Icon Bonnie Tyler Passes Away Following Medical Emergency</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0139-20-harsh-reality-checks-from-the-awful-everything-group-that.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0139-doctor-sends-alert-after-holding-out-for-a-hero-icon-bonnie-.jpg</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>41 Satisfying Petty Revenge Stories Where Cheaters Got What They Deserved</t>
+          <t>Hollywood’s Flawless-Look Obsession Slammed After “Unrealistic” Survival Scene Leaves Viewers Outraged</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0140-41-satisfying-petty-revenge-stories-where-cheaters-got-what-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0140-hollywoods-flawless-look-obsession-slammed-after-unrealistic.jpg</t>
         </is>
       </c>
     </row>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>“AITA For Telling My Family The Real Reason My Mother And I Are Not Attending My Sister’s Wedding?”</t>
+          <t>Erling Haaland’s Look Becomes Talking Point As Visagism Expert Drops Controversial Insights About His Image</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0141-aita-for-telling-my-family-the-real-reason-my-mother-and-i-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0141-erling-haalands-look-becomes-talking-point-as-visagism-exper.jpg</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gossip-Hungry MIL Snoops Through Confidential Files, Learns Attorney DIL Takes Privacy Seriously</t>
+          <t>Another Hollywood Romantic Age Gap Enrages Fans After Baby Announcement</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0142-gossip-hungry-mil-snoops-through-confidential-files-learns-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0142-another-hollywood-romantic-age-gap-enrages-fans-after-baby-a.jpg</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sister Assumes She Is Getting Pregnant Teen’s Baby Without Asking, Loses It When The Answer Is No</t>
+          <t>Mom Of Nolan Wells’ Friend, Who’s Also A Judge, Reveals Why He Was Allegedly Left Behind On Island</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0143-sister-assumes-she-is-getting-pregnant-teens-baby-without-as.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0143-mom-of-nolan-wells-friend-whos-also-a-judge-reveals-why-he-w.jpg</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Wife Spends Hours Dealing With Drunk Hubby’s Mess, Then Security Footage Changes Everything</t>
+          <t>Celebrity Birthdays Today, July 9, 2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0144-wife-spends-hours-dealing-with-drunk-hubbys-mess-then-securi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0144-celebrity-birthdays-today-july-9-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Woman Tries To Make Sis Feel Bad About Her Past Drinking Problems, Sis Gives Her A Reality Check</t>
+          <t>NYT Pips Hints, Answers For 09-July-2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0145-woman-tries-to-make-sis-feel-bad-about-her-past-drinking-pro.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0145-nyt-pips-hints-answers-for-09-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #083 (Jun 14, 2026)</t>
+          <t>Spelling Bee Hints, Answers For 09-July-2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0146-daily-guess-the-timeline-game-083-jun-14-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0146-spelling-bee-hints-answers-for-09-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>30 Father’s Day Gifts That Went Completely Off Script And Are Honestly So Much Better For It</t>
+          <t>NYT Mini Crossword Hints And Answers For 09-July-2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0147-30-fathers-day-gifts-that-went-completely-off-script-and-are.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0147-nyt-mini-crossword-hints-and-answers-for-09-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>75 Ironic Posts That Might Make You Chuckle</t>
+          <t>Wordle #1846: Hints &amp; Answer (Jul 9, 2026)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0148-75-ironic-posts-that-might-make-you-chuckle.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0148-wordle-1846-hints-answer-jul-9-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>85 Randomly Funny Memes You Probably Haven’t Seen Before</t>
+          <t>NYT Strands Hints And Answers For 09-July-2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0149-85-randomly-funny-memes-you-probably-havent-seen-before.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0149-nyt-strands-hints-and-answers-for-09-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>54 Public Monuments That Became Famous For All The Wrong Reasons</t>
+          <t>NYT Connections Hints And Answers For 09-July-2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0150-54-public-monuments-that-became-famous-for-all-the-wrong-rea.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0150-nyt-connections-hints-and-answers-for-09-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>81 People Share Photos That Are Almost Too Perfect To Be Real</t>
+          <t>Mitchel Musso: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0151-81-people-share-photos-that-are-almost-too-perfect-to-be-rea.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0151-mitchel-musso-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>“Here To Explain Everything”: 92 Facts And Stories You Might Not Have Heard Of Before</t>
+          <t>Rebecca Sugar: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0152-here-to-explain-everything-92-facts-and-stories-you-might-no.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0152-rebecca-sugar-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>41 Misconceptions And Outdated Beliefs People Proudly Corrected</t>
+          <t>Lindsey Graham: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0153-41-misconceptions-and-outdated-beliefs-people-proudly-correc.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0153-lindsey-graham-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>85 Feminist Posts That Say The Quiet Part Out Loud</t>
+          <t>Kevin O’Leary: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0154-85-feminist-posts-that-say-the-quiet-part-out-loud.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0154-kevin-oleary-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>“Why Aren’t Girls Into Me?”: 50 Real Reasons These Incels Are ‘Forever Alone,’ According To Their Friends</t>
+          <t>Pamela Adlon: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0155-why-arent-girls-into-me-50-real-reasons-these-incels-are-for.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0155-pamela-adlon-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>39 Things Americans Barely Notice That Stand Out To Foreign Visitors</t>
+          <t>Chris Cooper: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0156-39-things-americans-barely-notice-that-stand-out-to-foreign-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0156-chris-cooper-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>“Sickening”: 47 Times Women Deeply Regretted Looking Through Their Partner’s Phone</t>
+          <t>Jimmy Smits: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0157-sickening-47-times-women-deeply-regretted-looking-through-th.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0157-jimmy-smits-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Woman Is Asked To Help The Sister Who Slept With Her Boyfriend, Family Drama Follows</t>
+          <t>Jack White: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0158-woman-is-asked-to-help-the-sister-who-slept-with-her-boyfrie.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0158-jack-white-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>“My Girlfriend Broke Her Back. Her Parents’ Response Shocked Me”</t>
+          <t>Courtney Love: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0159-my-girlfriend-broke-her-back-her-parents-response-shocked-me.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0159-courtney-love-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Your Social Battery Has A Limit – These 27 Questions Reveal Exactly Where It Is</t>
+          <t>Tom Hanks: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0160-your-social-battery-has-a-limit-these-27-questions-reveal-ex.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0160-tom-hanks-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #029 (Jun 14, 2026)</t>
+          <t>Pamela Adlon: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0161-daily-guess-the-country-game-029-jun-14-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0161-pamela-adlon-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #027 (Jun 14, 2026)</t>
+          <t>Chris Cooper: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0162-daily-word-search-game-027-jun-14-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0162-chris-cooper-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #088 (Jun 14, 2026)</t>
+          <t>Jimmy Smits: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0163-daily-guess-the-famous-person-game-088-jun-14-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0163-jimmy-smits-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Daily Guess The Timeline Game #082 (Jun 13, 2026)</t>
+          <t>Courtney Love: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0164-daily-guess-the-timeline-game-082-jun-13-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0164-courtney-love-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>For Decades, Wives Paid A Mysterious Woman To Fix Their Marriage—Until A Guilt-Ridden Client Told Police All</t>
+          <t>Jack White: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0165-for-decades-wives-paid-a-mysterious-woman-to-fix-their-marri.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0165-jack-white-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>81 Designs So Bad That They Deserve To Be Named And Shamed Online (New Pics)</t>
+          <t>Tom Hanks: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0166-81-designs-so-bad-that-they-deserve-to-be-named-and-shamed-o.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0166-tom-hanks-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>67 Wholesome Internet Finds That Might Restore Your Faith In Humanity (New Pics)</t>
+          <t>Railway Conductor Who Went Viral With Independence Day Message To Passengers Faces Huge Karma In Major Update</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0167-67-wholesome-internet-finds-that-might-restore-your-faith-in.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0167-railway-conductor-who-went-viral-with-independence-day-messa.jpg</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Someone Asked For Wholesome Pics Of World Leaders, 35 People Share Their Favorites</t>
+          <t>Zendaya’s Latest Look Has Everyone Talking After Fans Spot One Tiny Detail: “You’re All So Shocked By This”</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0168-someone-asked-for-wholesome-pics-of-world-leaders-35-people-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0168-zendayas-latest-look-has-everyone-talking-after-fans-spot-on.jpg</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>‘The Weird Unknown’: 79 Creepy, Weird, And Intriguing Facts About The Ocean (New Pics)</t>
+          <t>Woman’s Cosmetic Procedure Goes Viral As Her Face Changes Dramatically, Expert Weighs In And Explains The Risks</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0169-the-weird-unknown-79-creepy-weird-and-intriguing-facts-about.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0169-womans-cosmetic-procedure-goes-viral-as-her-face-changes-dra.jpg</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>People Who Lived Through The 1990s And 2000s Are Thoroughly Enjoying These 121 Posts (New Pics)</t>
+          <t>Oncologist Reveals The Five Cancer Symptoms People Most Commonly Dismiss As Normal Aging Or Stress</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0170-people-who-lived-through-the-1990s-and-2000s-are-thoroughly-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0170-oncologist-reveals-the-five-cancer-symptoms-people-most-comm.jpg</t>
         </is>
       </c>
     </row>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>64 Urban Hell Photos That Have People Wondering How These Places Came To Be</t>
+          <t>Disney’s ‘Tangled’ Remake Under Fire After Leaked Set Photo Leaves Fans Appalled With Major Change</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0171-64-urban-hell-photos-that-have-people-wondering-how-these-pl.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0171-disneys-tangled-remake-under-fire-after-leaked-set-photo-lea.jpg</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>45 Times People Asked Dumb Science Questions And The Internet Delivered Perfect Answers</t>
+          <t>“Lonely” Man Makes Crying Plea And Exposes Tough Truth, Doctor Reacts</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0172-45-times-people-asked-dumb-science-questions-and-the-interne.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0172-lonely-man-makes-crying-plea-and-exposes-tough-truth-doctor-.jpg</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>65 Men Recall The Exact Moment Everything Fell Apart</t>
+          <t>After MAGA Support, Carrie Underwood Gets Mercilessly Taunted For Performance At Golf Course</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0173-65-men-recall-the-exact-moment-everything-fell-apart.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0173-after-maga-support-carrie-underwood-gets-mercilessly-taunted.jpg</t>
         </is>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>“We Don’t Believe Employees Should Own Pets”: 27 Bosses And Employers That Are Truly The Worst</t>
+          <t>Classic Porsche 911 Became Extraordinary Stained-Glass Sculpture In This Artist’s Hands</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0174-we-dont-believe-employees-should-own-pets-27-bosses-and-empl.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0174-classic-porsche-911-became-extraordinary-stained-glass-sculp.jpg</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3077,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>81 Funny Memes That People In Sales May Use To Explain What They Do To Their Families And Friends</t>
+          <t>Chilling Final Audio From Pilot Released As Rescue Efforts To Find Plane That Vanished Continue</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0175-81-funny-memes-that-people-in-sales-may-use-to-explain-what-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0175-chilling-final-audio-from-pilot-released-as-rescue-efforts-t.jpg</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Man Says His Girlfriend Won’t Allow Him To Enter One Room In Her House, Is Shocked To Learn The Truth</t>
+          <t>After Lookmaxxer’s Bizarre Passing At 32, His Extreme Transformation Stuns Many</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0176-man-says-his-girlfriend-wont-allow-him-to-enter-one-room-in-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0176-after-lookmaxxers-bizarre-passing-at-32-his-extreme-transfor.jpg</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bride Starts Having Doubts 9 Days Before The Wedding, Internet Pushes Her To Walk Away Now</t>
+          <t>Disgraced Hollywood Star Reportedly Breaks Down After His “Disgusting” Comeback Film Gets Unbanned</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0177-bride-starts-having-doubts-9-days-before-the-wedding-interne.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0177-disgraced-hollywood-star-reportedly-breaks-down-after-his-di.jpg</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Decide If These People Had A Valid Response In 10 Real-Life Situations</t>
+          <t>‘Looksmaxxer’ Loses His Life At 32 After Alleged Bizarre Incident</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0178-decide-if-these-people-had-a-valid-response-in-10-real-life-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0178-looksmaxxer-loses-his-life-at-32-after-alleged-bizarre-incid.jpg</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Daily Guess The Country Game #028 (Jun 13, 2026)</t>
+          <t>Celebrity Birthdays Today, July 8, 2026</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0179-daily-guess-the-country-game-028-jun-13-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0179-celebrity-birthdays-today-july-8-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #026 (Jun 13, 2026)</t>
+          <t>NYT Pips Hints, Answers For 08-July-2026</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0180-daily-word-search-game-026-jun-13-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0180-nyt-pips-hints-answers-for-08-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Daily Guess The Famous Person Game #087 (Jun 13, 2026)</t>
+          <t>Wordle #1845: Hints &amp; Answer (Jul 8, 2026)</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0181-daily-guess-the-famous-person-game-087-jun-13-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0181-wordle-1845-hints-answer-jul-8-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Man Reconnects With A Childhood Friend He Hasn’t Seen In 10 Years, Blows Up The Life He’s Built</t>
+          <t>NYT Mini Crossword Hints And Answers For 08-July-2026</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0182-man-reconnects-with-a-childhood-friend-he-hasnt-seen-in-10-y.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0182-nyt-mini-crossword-hints-and-answers-for-08-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bride Bans Sister’s Boyfriend From Wedding For Disgusting And Ridiculous Reasons</t>
+          <t>Spelling Bee Hints, Answers For 08-July-2026</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0183-bride-bans-sisters-boyfriend-from-wedding-for-disgusting-and.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0183-spelling-bee-hints-answers-for-08-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ben Stiller Faces Backlash After Viral Video Appears To Contradict His Message On Homelessness</t>
+          <t>NYT Connections Hints And Answers For 08-July-2026</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0184-ben-stiller-faces-backlash-after-viral-video-appears-to-cont.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0184-nyt-connections-hints-and-answers-for-08-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>40 Funny Pics Of Cats Being Themselves And Showing Off Their Shredded Masterpieces</t>
+          <t>NYT Strands Hints And Answers For 08-July-2026</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0185-40-funny-pics-of-cats-being-themselves-and-showing-off-their.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0185-nyt-strands-hints-and-answers-for-08-july-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>34 Scam Examples That Show America Is Living In A Completely Different Reality From Everyone Else</t>
+          <t>Wolfgang Puck: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0186-34-scam-examples-that-show-america-is-living-in-a-completely.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0186-wolfgang-puck-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>“Thank You Wave In Traffic”: 59 Social Contracts That Make Everyday Life Better</t>
+          <t>Sophia Bush: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0187-thank-you-wave-in-traffic-59-social-contracts-that-make-ever.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0187-sophia-bush-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3272,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Looksmaxxer Clavicular Just Had His 3rd Surgery, And People Are Getting Concerned About His Transformation</t>
+          <t>David Corenswet: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0188-looksmaxxer-clavicular-just-had-his-3rd-surgery-and-people-a.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0188-david-corenswet-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>“Do You Understand How The Body Works?”: Score 20/24 To Prove It In This Biology Quiz</t>
+          <t>Jaden Smith: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0189-do-you-understand-how-the-body-works-score-2024-to-prove-it-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0189-jaden-smith-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>59 Design Disasters That Are So Bad, They’re Honestly Kind Of Funny (New Pics)</t>
+          <t>Maya Hawke: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0190-59-design-disasters-that-are-so-bad-theyre-honestly-kind-of-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0190-maya-hawke-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>83 Examples Of “Awful Taste But Great Execution” That Left People Confused (New Pics)</t>
+          <t>Billy Crudup: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0191-83-examples-of-awful-taste-but-great-execution-that-left-peo.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0191-billy-crudup-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>46 Times People Heard Such Genius Insults They Memorized Them</t>
+          <t>Milo Ventimiglia: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0192-46-times-people-heard-such-genius-insults-they-memorized-the.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0192-milo-ventimiglia-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>63 Photos That Are So Great, They Deserve To Be Seen By More People</t>
+          <t>Beck: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0193-63-photos-that-are-so-great-they-deserve-to-be-seen-by-more-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0193-beck-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Bride’s Wedding Guests Start Canceling One By One, The Reason Why Leaves Her Speechless</t>
+          <t>Anjelica Huston: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0194-brides-wedding-guests-start-canceling-one-by-one-the-reason-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0194-anjelica-huston-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Woman Calls The Police After Learning What Her Sister Served For Lunch</t>
+          <t>Kevin Bacon: Bio And Career Highlights</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0195-woman-calls-the-police-after-learning-what-her-sister-served.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0195-kevin-bacon-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Toxic Fiancée Airs All Their Dirty Laundry, Guy’s Friends Finally Decide To Break Their Silence</t>
+          <t>Taylor Swift’s Response To Trump Post Leaves Fans Broiling As Backlash Over Controversial Wedding Mounts</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0196-toxic-fiancee-airs-all-their-dirty-laundry-guys-friends-fina.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0196-taylor-swifts-response-to-trump-post-leaves-fans-broiling-as.jpg</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>From Hidden Objects To Impossible Perspectives: Challenge Your Vision With 15 Image Riddles</t>
+          <t>Taylor Swift And Travis Kelce’s Wedding Guest Slammed Over “White” Dress Rule, Here’s The Verdict From Etiquette Experts</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0197-from-hidden-objects-to-impossible-perspectives-challenge-you.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0197-taylor-swift-and-travis-kelces-wedding-guest-slammed-over-wh.jpg</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Doctor Warns Of The Risks After “Looksmaxxer” Films Himself Using A Maxilla Expander</t>
+          <t>Man’s Suspected Brain Cancer Turns Into A Horror Story As Medical Team Uncovers Something Far Creepier</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0198-doctor-warns-of-the-risks-after-looksmaxxer-films-himself-us.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0198-mans-suspected-brain-cancer-turns-into-a-horror-story-as-med.jpg</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>29 Amazing Wall Transformations By Nuno Miles That Turn Urban Spaces Into Hyperrealistic Art</t>
+          <t>5YO Boy Undergoes Cosmetic Surgery — Mom’s Controversial Choice Raises Eyebrows But She Says She’d Repeat It</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0199-29-amazing-wall-transformations-by-nuno-miles-that-turn-urba.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0199-5yo-boy-undergoes-cosmetic-surgery-moms-controversial-choice.jpg</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,4512 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Daily Word Search Game #025 (Jun 12, 2026)</t>
+          <t>Woman Reveals She Removed Her Painful Breast Implants, And What Was Discovered Inside Left Her Speechless</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0200-daily-word-search-game-025-jun-12-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0200-woman-reveals-she-removed-her-painful-breast-implants-and-wh.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Videos Of Nolan Wells’ Last Moments Emerge After His Body Is Found And Friends’ Reactions Spur Racial Tensions</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0201-videos-of-nolan-wells-last-moments-emerge-after-his-body-is-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>“Historically Accurate” Age Gap In ‘The Odyssey’ Sparks Massive Uproar Over Disturbing Hollywood Practice</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0202-historically-accurate-age-gap-in-the-odyssey-sparks-massive-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>‘Odyssey’ Star Lupita Nyong’o Brutally Roasted Over The “Woke” Question She Says She’d Ask Homer</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0203-odyssey-star-lupita-nyongo-brutally-roasted-over-the-woke-qu.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Doctor Issues Urgent Warning After Ariana Grande Is Linked To Harmful Practice By Concerned Fans</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0204-doctor-issues-urgent-warning-after-ariana-grande-is-linked-t.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Lip Filler Controversy Catches Up To Millie Bobby Brown After “iPhone Face” Look In New Movie Explodes Online</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0205-lip-filler-controversy-catches-up-to-millie-bobby-brown-afte.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Plastic Surgeon Intervenes After Adele’s Appearance At Rare Public Outing Turns Into Viral Discussion</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0206-plastic-surgeon-intervenes-after-adeles-appearance-at-rare-p.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Taylor Swift And Travis Kelce’s Baby Plans Exposed With Intimate Details Of Married Life And Unexpected Dilemma</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0207-taylor-swift-and-travis-kelces-baby-plans-exposed-with-intim.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 7, 2026</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0208-celebrity-birthdays-today-july-7-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 07-July-2026</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0209-nyt-pips-hints-answers-for-07-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Wordle #1844: Hints &amp; Answer (Jul 7, 2026)</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0210-wordle-1844-hints-answer-jul-7-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 07-July-2026</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0211-nyt-strands-hints-and-answers-for-07-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 07-July-2026</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0212-nyt-mini-crossword-hints-and-answers-for-07-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 07-July-2026</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0213-spelling-bee-hints-answers-for-07-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 07-July-2026</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0214-nyt-connections-hints-and-answers-for-07-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sevyn Streeter: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0215-sevyn-streeter-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Ana Kasparian: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0216-ana-kasparian-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Cree Summer: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0217-cree-summer-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Bérénice Bejo: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0218-berenice-bejo-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Synyster Gates: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0219-synyster-gates-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Kirsten Vangsness: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0220-kirsten-vangsness-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Jorja Fox: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0221-jorja-fox-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Alesso: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0222-alesso-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Jim Gaffigan: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0223-jim-gaffigan-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Ringo Starr: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0224-ringo-starr-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Karoline Leavitt’s Marriage Under Fire After Viral Post Reveals Explosive Age Gap Between Husband And Her Mom</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0225-karoline-leavitts-marriage-under-fire-after-viral-post-revea.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>After Trump’s “Trolling” Taylor Swift During Her Wedding, Fans Expose Why They’re Disappointed With The Singer</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0226-after-trumps-trolling-taylor-swift-during-her-wedding-fans-e.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Biohacker Bryan Johnson Reveals Dreadful Diagnosis Despite Meticulous And Intense Health Regimen</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0227-biohacker-bryan-johnson-reveals-dreadful-diagnosis-despite-m.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Adele’s Appearance Becomes Latest Heated Topic Of Discussion After She’s Spotted In Public</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0228-adeles-appearance-becomes-latest-heated-topic-of-discussion-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 6, 2026</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0229-celebrity-birthdays-today-july-6-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 06-July-2026</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0230-nyt-pips-hints-answers-for-06-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Wordle #1843: Hints &amp; Answer (Jul 6, 2026)</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0231-wordle-1843-hints-answer-jul-6-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 06-July-2026</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0232-nyt-strands-hints-and-answers-for-06-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 06-July-2026</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0233-spelling-bee-hints-answers-for-06-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 06-July-2026</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0234-nyt-mini-crossword-hints-and-answers-for-06-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 06-July-2026</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0235-nyt-connections-hints-and-answers-for-06-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>David Karp: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0236-david-karp-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Geoffrey Rush: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0237-geoffrey-rush-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Ludwig Ahgren: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0238-ludwig-ahgren-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Eva Green: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0239-eva-green-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tamera Mowry: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0240-tamera-mowry-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Tia Mowry: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0241-tia-mowry-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>George W. Bush: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0242-george-w-bush-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>50 Cent: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0243-50-cent-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sylvester Stallone: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0244-sylvester-stallone-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Kevin Hart: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0245-kevin-hart-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Ryan Reynolds Steps Away From Taylor Swift Wedding Drama As Blake Lively Reportedly Fumes</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0246-ryan-reynolds-steps-away-from-taylor-swift-wedding-drama-as-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Only Two Women Wore Jonathan Anderson Couture Before Taylor Swift, And Here Are Their Dresses</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0247-only-two-women-wore-jonathan-anderson-couture-before-taylor-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>The Best And The Worst-Dressed Celebrities At Taylor Swift’s Wedding</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0248-the-best-and-the-worst-dressed-celebrities-at-taylor-swifts-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 5, 2026</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0249-celebrity-birthdays-today-july-5-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 05-July-2026</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0250-nyt-pips-hints-answers-for-05-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 05-July-2026</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0251-spelling-bee-hints-answers-for-05-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 05-July-2026</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0252-nyt-mini-crossword-hints-and-answers-for-05-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Wordle #1842: Hints &amp; Answer (Jul 5, 2026)</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0253-wordle-1842-hints-answer-jul-5-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 05-July-2026</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0254-nyt-connections-hints-and-answers-for-05-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 05-July-2026</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0255-nyt-strands-hints-and-answers-for-05-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Danay Garcia: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0256-danay-garcia-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Jeon Jong-seo: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0257-jeon-jong-seo-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Nardwuar: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0258-nardwuar-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Dave Haywood: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0259-dave-haywood-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Ronald D. Moore: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0260-ronald-d-moore-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Jason Dolley: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0261-jason-dolley-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Pauly D: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0262-pauly-d-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Huey Lewis: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0263-huey-lewis-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>RZA: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0264-rza-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Edie Falco: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0265-edie-falco-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Adult Star Says Most Of The Men She Films With Have One ‘Unexpected’ Thing In Common</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0266-adult-star-says-most-of-the-men-she-films-with-have-one-unex.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>48 “Ugly Ducklings” Share The Incredible Transformations That Made Them Love Themselves</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0267-48-ugly-ducklings-share-the-incredible-transformations-that-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Taylor Swift Says “I Do” In A Stunning Christian Dior Haute Couture Wedding Dress</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0268-taylor-swift-says-i-do-in-a-stunning-christian-dior-haute-co.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Woman’s Post-Plastic Surgery Photos Divide The Internet As She And Her Surgeon Celebrate The Results</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0269-womans-post-plastic-surgery-photos-divide-the-internet-as-sh.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>5 Celebrities Whose BBL Stories Took A Turn Nobody Expected</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0270-5-celebrities-whose-bbl-stories-took-a-turn-nobody-expected.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 4, 2026</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0271-celebrity-birthdays-today-july-4-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 04-July-2026</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0272-nyt-pips-hints-answers-for-04-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Wordle #1841: Hints &amp; Answer (Jul 4, 2026)</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0273-wordle-1841-hints-answer-jul-4-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 04-July-2026</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0274-spelling-bee-hints-answers-for-04-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 04-July-2026</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0275-nyt-strands-hints-and-answers-for-04-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 04-July-2026</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0276-nyt-mini-crossword-hints-and-answers-for-04-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 04-July-2026</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0277-nyt-connections-hints-and-answers-for-04-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Victoria Abril: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0278-victoria-abril-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>John Waite: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0279-john-waite-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Melanie Fiona: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0280-melanie-fiona-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Richard Garriott: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0281-richard-garriott-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Elie Saab: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0282-elie-saab-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Angelique Boyer: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0283-angelique-boyer-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Michael “The Situation” Sorrentino: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0284-michael-the-situation-sorrentino-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Geraldo Rivera: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0285-geraldo-rivera-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Eva Marie Saint: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0286-eva-marie-saint-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Post Malone: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0287-post-malone-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Bonnie Blue Back In Spotlight After Baby Shower Scandal As 1000th Man From “Crazy” Event Speaks Out</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0288-bonnie-blue-back-in-spotlight-after-baby-shower-scandal-as-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>14-Year-Old Boy Arrested Twice After Being Accused Of Terrorizing Tourists With Water Toy In Controversial Case</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0289-14-year-old-boy-arrested-twice-after-being-accused-of-terror.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Millie Bobby Brown Angers Fans By Jumping On Sheer Look Bandwagon: “Hollywood Ruins Them Young”</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0290-millie-bobby-brown-angers-fans-by-jumping-on-sheer-look-band.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Video Of Influencer Working Out In A Bikini Is Gaining Attention Again After Netizens Spot One Sickening Detail</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0291-video-of-influencer-working-out-in-a-bikini-is-gaining-atten.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Silo Season 3 Cast Guide: Every New And Returning Character</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0292-silo-season-3-cast-guide-every-new-and-returning-character.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Expert Reveals The Celebs Who Have Devalued Their Homes With ‘Questionable’ Renovations</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0293-expert-reveals-the-celebs-who-have-devalued-their-homes-with.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Therapist Warns Teens Are Losing One Personality Trait That Shapes Future</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0294-therapist-warns-teens-are-losing-one-personality-trait-that-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Kim Kardashian’s Brand Now Sells A “Micro Bikini” But It’s Quickly Backfiring</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0295-kim-kardashians-brand-now-sells-a-micro-bikini-but-its-quick.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>11-Year-Old Canadian Boy Tragically Loses His Life After Being Woken Up By A Bat On His Face</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0296-11-year-old-canadian-boy-tragically-loses-his-life-after-bei.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Millie Bobby Brown Breaks Silence After Getting Brutally Roasted Over Major Blunder In ‘Enola Holmes 3’</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0297-millie-bobby-brown-breaks-silence-after-getting-brutally-roa.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Actress’s Past Transformation Resurfaces, Sparking Heated Discussion About How Men Criticize Women’s Appearances</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0298-actresss-past-transformation-resurfaces-sparking-heated-disc.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Absurd Reason Police Allowed ‘Worst Neighbor Ever’ To Mow Lawn Shirtless Before Fatal Incident Revealed</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0299-absurd-reason-police-allowed-worst-neighbor-ever-to-mow-lawn.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 3, 2026</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0300-celebrity-birthdays-today-july-3-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 03-July-2026</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0301-nyt-pips-hints-answers-for-03-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Wordle #1840: Hints &amp; Answer (Jul 3, 2026)</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0302-wordle-1840-hints-answer-jul-3-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 03-July-2026</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0303-nyt-strands-hints-and-answers-for-03-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 03-July-2026</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0304-nyt-connections-hints-and-answers-for-03-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 03-July-2026</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0305-nyt-mini-crossword-hints-and-answers-for-03-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 03-July-2026</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0306-spelling-bee-hints-answers-for-03-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Connie Nielsen: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0307-connie-nielsen-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Benedict Wong: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0308-benedict-wong-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Julian Assange: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0309-julian-assange-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Montel Williams: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0310-montel-williams-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Yeardley Smith: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0311-yeardley-smith-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Audra McDonald: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0312-audra-mcdonald-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Elle King: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0313-elle-king-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Patrick Wilson: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0314-patrick-wilson-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Olivia Munn: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0315-olivia-munn-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Tom Cruise: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0316-tom-cruise-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Major Update In Empire State Building Daredevil Case As NYPD Footage Reveals Moments Leading To Their Arrest</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0317-major-update-in-empire-state-building-daredevil-case-as-nypd.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Disturbing Walmart Parking Lot Video Shows Army Veteran’s Horrific End After Furious Dispute With Woman</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0318-disturbing-walmart-parking-lot-video-shows-army-veterans-hor.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Wil Wheaton Joins Backlash Against “Coward” Dwayne “The Rock” Johnson Over His Stance On Political Topics</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0319-wil-wheaton-joins-backlash-against-coward-dwayne-the-rock-jo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Collin Gosselin Breaks Silence On The “Disturbing” Truth Led Mom To Send Him To A Behavioral Facility At 12</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0320-collin-gosselin-breaks-silence-on-the-disturbing-truth-led-m.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Silo Season 3: Release Date, Cast, Plot, And Streaming Details</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0321-silo-season-3-release-date-cast-plot-and-streaming-details.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Olivia Wilde Sparks Concern As She Shows Off Dramatically Slimmer Frame Following “Medical Cadaver” Backlash</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0322-olivia-wilde-sparks-concern-as-she-shows-off-dramatically-sl.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Trump Posts Unhinged Video With Him As A Doctor Diagnosing Different Celebrities With Derangement Syndrome</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0323-trump-posts-unhinged-video-with-him-as-a-doctor-diagnosing-d.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>“Cancel It Immediately!”: Colleen Hoover Faces Brutal Backlash Over Shocking New Amazon Deal As Fans Expose Her Dark Past</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0324-cancel-it-immediately-colleen-hoover-faces-brutal-backlash-o.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Major Hollywood Star Blows Fans Away With “Unrecognizable” Look In New Photo</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0325-major-hollywood-star-blows-fans-away-with-unrecognizable-loo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Expert Weighs In After Viral Video Of Woman Shaving Her Face Sparks Heated Debate</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0326-expert-weighs-in-after-viral-video-of-woman-shaving-her-face.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Gal Gadot’s Career Takes Another Hit As New Netflix Film Is Blasted As One Of The Year’s Worst: “Get Her Off The Screen”</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0327-gal-gadots-career-takes-another-hit-as-new-netflix-film-is-b.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>8 Buddhist Monks Lose Their Lives And Dozens More Are Injured After 11YO Boy Rams Them With Dad’s Pickup Truck</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0328-8-buddhist-monks-lose-their-lives-and-dozens-more-are-injure.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>This Photographer Uses A Smartphone To Reveal The Magical World Of Tiny Insects (32 Pics)</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0329-this-photographer-uses-a-smartphone-to-reveal-the-magical-wo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Man’s “Unhinged” Voice Memo Ultimatum To Woman After One Date Has People Bemoaning Modern Dating</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0330-mans-unhinged-voice-memo-ultimatum-to-woman-after-one-date-h.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>A Teacher Told Her She Had No Artistic Talent, Now She Creates These Incredible Cotton Wool Sculptures (33 Pics)</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0331-a-teacher-told-her-she-had-no-artistic-talent-now-she-create.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Artist Combines Vintage Knitting Machines And Digital Art To Create Stunning Portraits (33 Pics)</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0332-artist-combines-vintage-knitting-machines-and-digital-art-to.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 2, 2026</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0333-celebrity-birthdays-today-july-2-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Wordle #1839: Hints &amp; Answer (Jul 2, 2026)</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0334-wordle-1839-hints-answer-jul-2-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 02-July-2026</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0335-spelling-bee-hints-answers-for-02-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 02-July-2026</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0336-nyt-connections-hints-and-answers-for-02-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 02-July-2026</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0337-nyt-pips-hints-answers-for-02-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 02-July-2026</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0338-nyt-mini-crossword-hints-and-answers-for-02-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 02-July-2026</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0339-nyt-strands-hints-and-answers-for-02-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Elise Stefanik: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0340-elise-stefanik-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Elizabeth Reaser: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0341-elizabeth-reaser-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Jerry Hall: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0342-jerry-hall-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Michelle Branch: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0343-michelle-branch-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Ashley Tisdale: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0344-ashley-tisdale-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Vince Staples: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0345-vince-staples-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Saweetie: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0346-saweetie-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Larry David: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0347-larry-david-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Lindsay Lohan: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0348-lindsay-lohan-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Margot Robbie: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0349-margot-robbie-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Empire State Building Daredevils Expose Security Lapse After Scaling 1,454-Foot Antenna To Hang “Cringe” Flag</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0350-empire-state-building-daredevils-expose-security-lapse-after.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Looksmaxxing Influencer Clavicular Triggers Chaos After Mistaking Young Woman For Adult Star Lily Phillips</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0351-looksmaxxing-influencer-clavicular-triggers-chaos-after-mist.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Ari Fletcher’s BBL Sparks Frenzy After Fans Spot It Hanging Off Chair Backstage At BET Awards</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0352-ari-fletchers-bbl-sparks-frenzy-after-fans-spot-it-hanging-o.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>After Danny Glover’s Harrowing Diagnosis Reveal, Doctor Shares Warning Symptoms</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0353-after-danny-glovers-harrowing-diagnosis-reveal-doctor-shares.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Fans Can’t Ignore Hollywood’s “Plastic Surgery Blindness” After Nepo Baby’s Shocking Transformation</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0354-fans-cant-ignore-hollywoods-plastic-surgery-blindness-after-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Bonnie Blue Follows Up Grotesque Baby Shower With “Bump Update” Aimed At Her Critics</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0355-bonnie-blue-follows-up-grotesque-baby-shower-with-bump-updat.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>New Jersey Middle School Forced To Recall Yearbook And Launch Investigation After Baby Photo Sparks Uproar</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0356-new-jersey-middle-school-forced-to-recall-yearbook-and-launc.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Millie Bobby Brown’s Co-Star Sparks Furious Misogyny Backlash After Shady Dig: “Very Unpleasant Guy”</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0357-millie-bobby-browns-co-star-sparks-furious-misogyny-backlash.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Kate Gosselin Viciously Claps Back After Son Collin Makes Horrifying Claims About His Childhood</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0358-kate-gosselin-viciously-claps-back-after-son-collin-makes-ho.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, July 1, 2026</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0359-celebrity-birthdays-today-july-1-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 01-July-2026</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0360-nyt-mini-crossword-hints-and-answers-for-01-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 01-July-2026</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0361-nyt-connections-hints-and-answers-for-01-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 01-July-2026</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0362-nyt-pips-hints-answers-for-01-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 01-July-2026</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0363-spelling-bee-hints-answers-for-01-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 01-July-2026</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0364-nyt-strands-hints-and-answers-for-01-july-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Wordle #1838: Hints &amp; Answer (Jul 1, 2026)</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0365-wordle-1838-hints-answer-jul-1-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>37 Random Photos That Look Completely Made-Up And Senseless, But Are Quite Amusing Anyway</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0366-37-random-photos-that-look-completely-made-up-and-senseless-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Léa Seydoux: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0367-lea-seydoux-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Storm Reid: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0368-storm-reid-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Alan Ruck: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0369-alan-ruck-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Chloe Bailey: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0370-chloe-bailey-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Tate McRae: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0371-tate-mcrae-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Dan Aykroyd: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0372-dan-aykroyd-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Debbie Harry: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0373-debbie-harry-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Liv Tyler: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0374-liv-tyler-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Pamela Anderson: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0375-pamela-anderson-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Missy Elliott: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0376-missy-elliott-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Friend Reveals Mom-Of-Five’s Chilling Final Moments As She Fought To Survive Brutal Attack By Smiling Sisters</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0377-friend-reveals-mom-of-fives-chilling-final-moments-as-she-fo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Collin Gosselin Slams Mom For Praying “To God To Stop Hitting Me” When He Was 2 As Public Battle Intensifies</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0378-collin-gosselin-slams-mom-for-praying-to-god-to-stop-hitting.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Shania Twain Compared To Madonna Over Sheer Look And “Cringe” Dance Moves: “Does She Have No Dignity?”</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0379-shania-twain-compared-to-madonna-over-sheer-look-and-cringe-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Enola Holmes 3: Release Date, Time, And Plot For Millie Bobby Brown’s Netflix Movie</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0380-enola-holmes-3-release-date-time-and-plot-for-millie-bobby-b.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Elliot Page Shows Off Shredded Physique As He Reveals Getting “Hooked” On Boxing</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0381-elliot-page-shows-off-shredded-physique-as-he-reveals-gettin.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Media Personality Makes Bedroom Confession That Has Women All Agreeing</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0382-media-personality-makes-bedroom-confession-that-has-women-al.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Confused Fans Battle Over AMC Show As Star Shatters Internet With Unreal Shirtless Scene: “Her Waist?!”</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0383-confused-fans-battle-over-amc-show-as-star-shatters-internet.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>John Cena Shocks With Hair Transplant Reveal After Being Caught Having Trouble Walking</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0384-john-cena-shocks-with-hair-transplant-reveal-after-being-cau.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>‘Most Beautiful Girl In The World’ Thylane Blondeau Wedding To French DJ Sparks Fierce Fan Backlash: “No Grace”</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0385-most-beautiful-girl-in-the-world-thylane-blondeau-wedding-to.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Dangerous Social Media Challenge Makes Another Victim After Girl, 15, Loses Her Life</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0386-dangerous-social-media-challenge-makes-another-victim-after-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, June 30, 2026</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0387-celebrity-birthdays-today-june-30-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Wordle #1837: Hints &amp; Answer (Jun 30, 2026)</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0388-wordle-1837-hints-answer-jun-30-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 30-June-2026</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0389-nyt-mini-crossword-hints-and-answers-for-30-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 30-June-2026</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0390-nyt-pips-hints-answers-for-30-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 30-June-2026</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0391-spelling-bee-hints-answers-for-30-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 30-June-2026</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0392-nyt-strands-hints-and-answers-for-30-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 30-June-2026</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0393-nyt-connections-hints-and-answers-for-30-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Monica Potter: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0394-monica-potter-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Murray Cook: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0395-murray-cook-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Katherine Ryan: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0396-katherine-ryan-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Phil Anselmo: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0397-phil-anselmo-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>bbno$: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0398-bbno-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Jacksfilms: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0399-jacksfilms-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>David Alan Grier: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0400-david-alan-grier-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Lizzy Caplan: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0401-lizzy-caplan-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Fantasia Barrino: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0402-fantasia-barrino-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Vincent D’Onofrio: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0403-vincent-donofrio-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Kim Kardashian And Kanye Urged To “Protect Your Kids” After North’s “Sickening” Interactions With Adult Men</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0404-kim-kardashian-and-kanye-urged-to-protect-your-kids-after-no.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Man Covered In Blackout Tattoos Reveals Harsh Truths He Wishes He’d Known Before Diving Into The Trend</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0405-man-covered-in-blackout-tattoos-reveals-harsh-truths-he-wish.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Doctors Send Alert As Babies With Ear Muffs At World Cup Flood Social Media</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0406-doctors-send-alert-as-babies-with-ear-muffs-at-world-cup-flo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Woman Who Participated In Lily Phillips ‘Backdoor’ Challenge Claims Her Marriage Is In Shambles Now</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0407-woman-who-participated-in-lily-phillips-backdoor-challenge-c.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>5 Most Disturbing Moments From ‘House Of The Dragon’ After That “Disgusting” Intimate Scene</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0408-5-most-disturbing-moments-from-house-of-the-dragon-after-tha.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Frozen Body Known As “Green Boots” In Mount Everest Finally Identified After 30 Years</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0409-frozen-body-known-as-green-boots-in-mount-everest-finally-id.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Man Loses His Temper Amid Conversation About His Elderly Mom, And It Ends Tragically For His Wife And Daughter</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0410-man-loses-his-temper-amid-conversation-about-his-elderly-mom.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Matthew Simmonds Carves Breathtaking Miniature Architecture From Solid Stone (38 New Pics)</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0411-matthew-simmonds-carves-breathtaking-miniature-architecture-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Furious Fans Slam Major Netflix Show After Viral Casting Controversy Exposes Hidden Bias: “Now I Get It”</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0412-furious-fans-slam-major-netflix-show-after-viral-casting-con.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Biker Finds Baby Crawling Out At Night By Herself, Mom’s Motives Stun</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0413-biker-finds-baby-crawling-out-at-night-by-herself-moms-motiv.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Expert Issues Warning After Mom Shows Off Her 1-Year-Old Toddler’s Lunch</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0414-expert-issues-warning-after-mom-shows-off-her-1-year-old-tod.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Texas Sisters Cookie And Kitty Caught Grinning In Chilling Footage After Fatal Attack On Young Mom Of 5</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0415-texas-sisters-cookie-and-kitty-caught-grinning-in-chilling-f.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, June 29, 2026</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0416-celebrity-birthdays-today-june-29-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 29-June-2026</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0417-spelling-bee-hints-answers-for-29-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 29-June-2026</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0418-nyt-mini-crossword-hints-and-answers-for-29-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 29-June-2026</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0419-nyt-strands-hints-and-answers-for-29-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 29-June-2026</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0420-nyt-pips-hints-answers-for-29-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Wordle #1836: Hints &amp; Answer (Jun 29, 2026)</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0421-wordle-1836-hints-answer-jun-29-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 29-June-2026</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0422-nyt-connections-hints-and-answers-for-29-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Bret McKenzie: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0423-bret-mckenzie-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Luke Kirby: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0424-luke-kirby-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Sam Farrar: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0425-sam-farrar-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Lance Barber: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0426-lance-barber-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Melora Hardin: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0427-melora-hardin-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Lily Rabe: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0428-lily-rabe-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Gary Busey: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0429-gary-busey-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Colin Jost: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0430-colin-jost-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Nicole Scherzinger: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0431-nicole-scherzinger-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Camila Mendes: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0432-camila-mendes-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Kristen Stewart’s Cringe-Worthy Interaction Has Fans Calling Out One Man’s Invading Her Personal Space</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0433-kristen-stewarts-cringe-worthy-interaction-has-fans-calling-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Blue Ivy And North West’s Latest Appearances Reignite Debate Over Beyoncé And Kim Kardashian’s Parenting Styles</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0434-blue-ivy-and-north-wests-latest-appearances-reignite-debate-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>12 Donald Trump Moments That Sound Like Satire But Actually Happened</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0435-12-donald-trump-moments-that-sound-like-satire-but-actually-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, June 28, 2026</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0436-celebrity-birthdays-today-june-28-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Wordle #1835: Hints &amp; Answer (Jun 28, 2026)</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0437-wordle-1835-hints-answer-jun-28-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 28-June-2026</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0438-nyt-pips-hints-answers-for-28-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 28-June-2026</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0439-nyt-connections-hints-and-answers-for-28-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 28-June-2026</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0440-spelling-bee-hints-answers-for-28-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 28-June-2026</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0441-nyt-strands-hints-and-answers-for-28-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 28-June-2026</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0442-nyt-mini-crossword-hints-and-answers-for-28-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Alessandro Nivola: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0443-alessandro-nivola-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Kellie Pickler: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0444-kellie-pickler-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Tichina Arnold: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0445-tichina-arnold-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Markiplier: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0446-markiplier-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Chayanne: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0447-chayanne-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Mike White: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0448-mike-white-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>John Cusack: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0449-john-cusack-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Elon Musk: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0450-elon-musk-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Kathy Bates: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0451-kathy-bates-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Mel Brooks: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0452-mel-brooks-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>“Clearly Hates Him”: Will Smith And Jada Pinkett Smith’s Viral Clip Has Fans Asking Why They’re Still Married</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0453-clearly-hates-him-will-smith-and-jada-pinkett-smiths-viral-c.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Harry Styles Sparks Concern After Choking On Water And Collapsing Onstage During Scorching Heatwave</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0454-harry-styles-sparks-concern-after-choking-on-water-and-colla.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>6 Horrific Taylor Parker Case Details Too Disturbing For Netflix’s Maternal Instinct</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0455-6-horrific-taylor-parker-case-details-too-disturbing-for-net.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Days After ‘Implants Going Bad’ Backlash, Katy Perry Takes Aim At Ex Orlando Bloom In ‘Horrifying’ New Video</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0456-days-after-implants-going-bad-backlash-katy-perry-takes-aim-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Private Investigator Warns Homeowners About The One Thing They Should Stop Doing</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0457-private-investigator-warns-homeowners-about-the-one-thing-th.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, June 27, 2026</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0458-celebrity-birthdays-today-june-27-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 27-June-2026</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0459-nyt-pips-hints-answers-for-27-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 27-June-2026</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0460-nyt-strands-hints-and-answers-for-27-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 27-June-2026</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0461-spelling-bee-hints-answers-for-27-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Wordle #1834: Hints &amp; Answer (Jun 27, 2026)</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0462-wordle-1834-hints-answer-jun-27-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 27-June-2026</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0463-nyt-connections-hints-and-answers-for-27-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 27-June-2026</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0464-nyt-mini-crossword-hints-and-answers-for-27-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Chandler Riggs: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0465-chandler-riggs-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Matthew Lewis: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0466-matthew-lewis-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Bianca Del Rio: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0467-bianca-del-rio-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Sam Claflin: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0468-sam-claflin-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Ed Westwick: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0469-ed-westwick-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Vera Wang: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0470-vera-wang-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>H.E.R.: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0471-her-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>J. J. Abrams: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0472-j-j-abrams-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Khloé Kardashian: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0473-khloe-kardashian-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Tobey Maguire: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0474-tobey-maguire-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Doctors Explain The Viral ‘Sadness Trigger’ Syndrome Distressing Women</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0475-doctors-explain-the-viral-sadness-trigger-syndrome-distressi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Millie Bobby Brown’s Red Carpet Appearance Draws Harsh Criticism From Fans: “She Should Fire Her Stylist”</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0476-millie-bobby-browns-red-carpet-appearance-draws-harsh-critic.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Ariana Grande Fans Begging Her To Get Help After Viral Tour Video Sparks Major Concern</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0477-ariana-grande-fans-begging-her-to-get-help-after-viral-tour-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Woman Shares How Her Best Friend Digitally Kidnapped Her Daughter, Reveals The Messages That Changed Everything</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0478-woman-shares-how-her-best-friend-digitally-kidnapped-her-dau.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Hit With Brutal Backlash, ‘The Bear’ Finally Writes Out Its Most Insufferable Character In “Chaotic” Final Season</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0479-hit-with-brutal-backlash-the-bear-finally-writes-out-its-mos.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Entire ‘Hideous’ Timeline Of Bonnie Blue’s Baby Shower Is Exposed After Guests Reveal Secrets</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0480-entire-hideous-timeline-of-bonnie-blues-baby-shower-is-expos.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Mom Horrified By What She Hears After Hiding Audio Recorder In Son’s Backpack After Noticing Changed Behavior</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0481-mom-horrified-by-what-she-hears-after-hiding-audio-recorder-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Are Taylor Swift And Selena Gomez Pregnant At The Same Time? Fans Point To Signs In Videos</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0482-are-taylor-swift-and-selena-gomez-pregnant-at-the-same-time-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>A Psychologist Asked Dads What Their Wives Stopped Doing After Having Kids, And The Responses Got Heavy Fast</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0483-a-psychologist-asked-dads-what-their-wives-stopped-doing-aft.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>The Bear Season 5: Every Guest Star And Where We’ve Seen Them Before</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0484-the-bear-season-5-every-guest-star-and-where-weve-seen-them-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>This Illustrator Gives Doves Distinct Personalities In A Charming Series Inspired By A Real Rescue Bird (16 Pics)</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0485-this-illustrator-gives-doves-distinct-personalities-in-a-cha.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Rihanna’s Partner Accused Of Disrespecting Her Onstage With Racy Comment</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0486-rihannas-partner-accused-of-disrespecting-her-onstage-with-r.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>“Male Karen” Refuses To Move For 80YO Woman While “Relaxing” On Public Staircase And Filming Her</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0487-male-karen-refuses-to-move-for-80yo-woman-while-relaxing-on-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Influencer Facing The Firing Squad After Being Arrested In Dubai On Grave Charges</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0488-influencer-facing-the-firing-squad-after-being-arrested-in-d.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Doctor Discovers Jaw‑Dropping Surprise Hidden In Four‑Year‑Old Boy’s Plaster Cast</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0489-doctor-discovers-jawdropping-surprise-hidden-in-fouryearold-.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Celebrity Birthdays Today, June 26, 2026</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0490-celebrity-birthdays-today-june-26-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>NYT Pips Hints, Answers For 26-June-2026</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0491-nyt-pips-hints-answers-for-26-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>NYT Connections Hints And Answers For 26-June-2026</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0492-nyt-connections-hints-and-answers-for-26-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Spelling Bee Hints, Answers For 26-June-2026</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0493-spelling-bee-hints-answers-for-26-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>NYT Strands Hints And Answers For 26-June-2026</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0494-nyt-strands-hints-and-answers-for-26-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Wordle #1833: Hints &amp; Answer (Jun 26, 2026)</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0495-wordle-1833-hints-answer-jun-26-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>NYT Mini Crossword Hints And Answers For 26-June-2026</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0496-nyt-mini-crossword-hints-and-answers-for-26-june-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Patty Smyth: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0497-patty-smyth-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Gretchen Wilson: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0498-gretchen-wilson-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Jason Schwartzman: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0499-jason-schwartzman-bio-and-career-highlights.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Chris Isaak: Bio And Career Highlights</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0500-chris-isaak-bio-and-career-highlights.jpg</t>
         </is>
       </c>
     </row>
@@ -3663,6 +8163,306 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId500"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Groom Promises All 3 Sisters Bridesmaid Dresses, Bride Hands Out Rejection Letters Based On Weight</t>
+          <t>Sister Learns She’s No Longer In Brother’s Wedding Party, Heartbroken By Bride’s Explanation</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0020-groom-promises-all-3-sisters-bridesmaid-dresses-bride-hands-.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0020-sister-learns-shes-no-longer-in-brothers-wedding-party-heart.jpg</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Entitled Influencers Try To Use Luxe Hotel For Insta Pics, Badmouth The Venue When They’re Sent Home</t>
+          <t>Influencers Want Five-Star Content On A Zero-Star Budget, Luxury Hotel Finally Stops Playing Along</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0021-entitled-influencers-try-to-use-luxe-hotel-for-insta-pics-ba.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0021-influencers-want-five-star-content-on-a-zero-star-budget-lux.jpg</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Student Blames Everyone Around But Himself In His Failures, Demands A Solo Project And Fails Again</t>
+          <t>Stubborn Student Refuses To Work In A Group Despite Professor’s Warnings, Regrets It When He Fails</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0022-student-blames-everyone-around-but-himself-in-his-failures-d.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0022-stubborn-student-refuses-to-work-in-a-group-despite-professo.jpg</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>77 Quick, Clever, And Unexpected Comics From Joe Lennon (New Pics)</t>
+          <t>Life Is Weird And Hilarious: 77 New One-Panel Comics From Joe Lennon</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0023-77-quick-clever-and-unexpected-comics-from-joe-lennon-new-pi.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0023-life-is-weird-and-hilarious-77-new-one-panel-comics-from-joe.jpg</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Boyfriend Secretly Blocks Woman’s Male Friends On Facebook, Claims It’s Just Being “Protective”</t>
+          <t>BF Thinks He’s Entitled To Block GF’s Male Friends On Her Behalf, Fumes As She Leaves Him Over It</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0024-boyfriend-secretly-blocks-womans-male-friends-on-facebook-cl.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0024-bf-thinks-hes-entitled-to-block-gfs-male-friends-on-her-beha.jpg</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Struggling Dad Blames Wife For Sixth Pregnancy, Brother Gives Him A Brutal Reality Check</t>
+          <t>Bro Refuses To Sit Quietly While His Sibling Blames His Wife For Their Sixth Child And Money Woes</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0025-struggling-dad-blames-wife-for-sixth-pregnancy-brother-gives.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0025-bro-refuses-to-sit-quietly-while-his-sibling-blames-his-wife.jpg</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IT Worker Takes Down Buffoon Accountant With Clever Plan, Says “Network’s Down” Right Back At Her</t>
+          <t>Accounting Manager Turns IT Guy’s Work Life Into A Nightmare, His Epic Revenge Leaves Her Jobless</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0026-it-worker-takes-down-buffoon-accountant-with-clever-plan-say.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0026-accounting-manager-turns-it-guys-work-life-into-a-nightmare-.jpg</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From Sand To Packaging, Here Are 34 Unpopular Industries That Actually Make Millions</t>
+          <t>34 Secretive And Weird Billion-Dollar Industries Revealed Online That Most People Never Hear About</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0028-from-sand-to-packaging-here-are-34-unpopular-industries-that.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0028-34-secretive-and-weird-billion-dollar-industries-revealed-on.jpg</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Woman Serves Mean Teammates The Best Brownies Ever, Keeps Her Recipe Secret As Petty Payback</t>
+          <t>Woman Serves Horrible Teammates Amazing Brownies, Keeps The Secret Locked Up As The Best Payback</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0029-woman-serves-mean-teammates-the-best-brownies-ever-keeps-her.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0029-woman-serves-horrible-teammates-amazing-brownies-keeps-the-s.jpg</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wordle #1851: Hints &amp; Answer (Jul 14, 2026)</t>
+          <t>Wordle #1852: Hints &amp; Answer (Jul 15, 2026)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1851-hints-answer-jul-14-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1852-hints-answer-jul-15-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,8 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Striking Comparison Between Charlize Theron And Anne Hathaway Provokes Discussion On Beauty Standards</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0112-striking-comparison-between-charlize-theron-and-anne-hathawa.jpg</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8074,395 +8066,394 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId499"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -2130,8 +2130,16 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Striking Comparison Between Charlize Theron And Anne Hathaway Provokes Discussion On Beauty Standards</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0112-striking-comparison-between-charlize-theron-and-anne-hathawa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3847,16 +3855,8 @@
       <c r="A228" t="n">
         <v>227</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Biohacker Bryan Johnson Reveals Dreadful Diagnosis Despite Meticulous And Intense Health Regimen</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0227-biohacker-bryan-johnson-reveals-dreadful-diagnosis-despite-m.jpg</t>
-        </is>
-      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -8066,121 +8066,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId229"/>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -690,16 +690,8 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24 Award-Winning Wildlife Photos Shared By The Artist Gallery</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0016-24-award-winning-wildlife-photos-shared-by-the-artist-galler.jpg</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1007,12 +999,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wordle #1852: Hints &amp; Answer (Jul 15, 2026)</t>
+          <t>Wordle #1854: Hints &amp; Answer (Jul 17, 2026)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1852-hints-answer-jul-15-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1854-hints-answer-jul-17-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -3855,8 +3847,16 @@
       <c r="A228" t="n">
         <v>227</v>
       </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Biohacker Bryan Johnson Reveals Dreadful Diagnosis Despite Meticulous And Intense Health Regimen</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0227-biohacker-bryan-johnson-reveals-dreadful-diagnosis-despite-m.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7970,217 +7970,217 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId229"/>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -690,8 +690,16 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24 Award-Winning Wildlife Photos Shared By The Artist Gallery</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0016-24-award-winning-wildlife-photos-shared-by-the-artist-galler.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -999,12 +1007,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wordle #1854: Hints &amp; Answer (Jul 17, 2026)</t>
+          <t>Wordle #1855: Hints &amp; Answer (Jul 18, 2026)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1854-hints-answer-jul-17-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1855-hints-answer-jul-18-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -7970,490 +7978,491 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId500"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pins/pin_links.xlsx
+++ b/pins/pin_links.xlsx
@@ -570,16 +570,8 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Adult Star Bonnie Blue Describes How Participants Dealt With Her Baby Bump During 10-Hour July 4 Event</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0008-adult-star-bonnie-blue-describes-how-participants-dealt-with.jpg</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1007,12 +999,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wordle #1855: Hints &amp; Answer (Jul 18, 2026)</t>
+          <t>Wordle #1857: Hints &amp; Answer (Jul 20, 2026)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1855-hints-answer-jul-18-2026.jpg</t>
+          <t>https://raw.githubusercontent.com/Arslan0070/Pins/main/pins/0037-wordle-1857-hints-answer-jul-20-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -7970,499 +7962,498 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId499"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
